--- a/new original/_Lang_Chinese/Lang/CN/Dialog/Drama/quru.xlsx
+++ b/new original/_Lang_Chinese/Lang/CN/Dialog/Drama/quru.xlsx
@@ -758,7 +758,7 @@
     <t xml:space="preserve">……如果那首歌传开了就麻烦了……对了，那首歌的题材其实根本不存在。梦幻天蓝郁金香，听着就很假不是吗？连孩子都不会相信有那种花。真是糟糕的歌啊，哈哈！</t>
   </si>
   <si>
-    <t xml:space="preserve">…哎？</t>
+    <t xml:space="preserve">…诶？</t>
   </si>
   <si>
     <t xml:space="preserve">…罗伊特尔你个笨蛋！</t>

--- a/new original/_Lang_Chinese/Lang/CN/Dialog/Drama/quru.xlsx
+++ b/new original/_Lang_Chinese/Lang/CN/Dialog/Drama/quru.xlsx
@@ -2,25 +2,25 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <fileVersion appName="Calc"/>
-  <workbookPr autoCompressPictures="1"/>
-  <workbookProtection lockStructure="0" lockWindows="0" lockRevision="0"/>
+  <workbookPr backupFile="false" showObjects="all" date1904="false"/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView windowWidth="16384" windowHeight="8192" tabRatio="500"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="quru" sheetId="1" r:id="rId3"/>
+    <sheet name="quru" sheetId="1" state="visible" r:id="rId3"/>
   </sheets>
-  <calcPr calcMode="auto" fullCalcOnLoad="0" refMode="R1C1" iterate="0" iterateCount="100" iterateDelta="0.001" fullPrecision="1" calcCompleted="0" calcOnSave="0" concurrentCalc="0" forceFullCalc="0"/>
+  <calcPr iterateCount="100" refMode="R1C1" iterate="false" iterateDelta="0.001"/>
   <extLst>
-    <ext uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
-      <loext:extCalcPr xmlns:loext="http://schemas.libreoffice.org/" stringRefSyntax="CalcA1"/>
+    <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
+      <loext:extCalcPr stringRefSyntax="CalcA1"/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="369" uniqueCount="266">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="267" uniqueCount="192">
   <si>
     <t xml:space="preserve">step</t>
   </si>
@@ -721,242 +721,6 @@
   <si>
     <t xml:space="preserve">Ask "Kettle." It seems he is hiding many secrets from you all... Heh heh heh...</t>
   </si>
-  <si>
-    <t xml:space="preserve"/>
-  </si>
-  <si>
-    <t xml:space="preserve">怎么？</t>
-  </si>
-  <si>
-    <t xml:space="preserve">哼哼哼♪</t>
-  </si>
-  <si>
-    <t xml:space="preserve">唔，这欢快的哼歌声是从哪里来的…</t>
-  </si>
-  <si>
-    <t xml:space="preserve">呵呵，你很开心嘛，库罗茨亚。那是什么歌？</t>
-  </si>
-  <si>
-    <t xml:space="preserve">（无视）哼哼哼♪天蓝色的～♪</t>
-  </si>
-  <si>
-    <t xml:space="preserve">（嘎）</t>
-  </si>
-  <si>
-    <t xml:space="preserve">库罗茨亚，那首歌……是法莉斯小姐教给你的么？</t>
-  </si>
-  <si>
-    <t xml:space="preserve">哼哼哼♪梦幻的～♪</t>
-  </si>
-  <si>
-    <t xml:space="preserve">不、不要啊…！</t>
-  </si>
-  <si>
-    <t xml:space="preserve">啊，不、不对…呃，不是说你唱得不好。只是那首歌实在是…</t>
-  </si>
-  <si>
-    <t xml:space="preserve">……如果那首歌传开了就麻烦了……对了，那首歌的题材其实根本不存在。梦幻天蓝郁金香，听着就很假不是吗？连孩子都不会相信有那种花。真是糟糕的歌啊，哈哈！</t>
-  </si>
-  <si>
-    <t xml:space="preserve">…诶？</t>
-  </si>
-  <si>
-    <t xml:space="preserve">…罗伊特尔你个笨蛋！</t>
-  </si>
-  <si>
-    <t xml:space="preserve">啊，等、等等库罗茨亚，别露出那么生气的表情…等、等下啊…！</t>
-  </si>
-  <si>
-    <t xml:space="preserve">难道…那个孩子真的相信有梦幻天蓝郁金香吗？不会吧……</t>
-  </si>
-  <si>
-    <t xml:space="preserve">摸摸，摸摸♪</t>
-  </si>
-  <si>
-    <t xml:space="preserve">姆啾！</t>
-  </si>
-  <si>
-    <t xml:space="preserve">嘿嘿，很痒吗，歌罗贡？</t>
-  </si>
-  <si>
-    <t xml:space="preserve">姆啾。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">摸摸，摸摸，摸摸，摸摸，摸摸♪</t>
-  </si>
-  <si>
-    <t xml:space="preserve">姆啾…姆啾！</t>
-  </si>
-  <si>
-    <t xml:space="preserve">嘿嘿，很痒吧，歌罗贡！</t>
-  </si>
-  <si>
-    <t xml:space="preserve">啊…？</t>
-  </si>
-  <si>
-    <t xml:space="preserve">有人的感觉…那边有人过来了。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">谁会在这个时间来呢？</t>
-  </si>
-  <si>
-    <t xml:space="preserve">此处是…</t>
-  </si>
-  <si>
-    <t xml:space="preserve">姆啾…？</t>
-  </si>
-  <si>
-    <t xml:space="preserve">…龙之子，还有灾眼的少女…这是怎么回事…？</t>
-  </si>
-  <si>
-    <t xml:space="preserve">那个男人…斗篷下面诡异的眼睛，不是人类……异形……
-歌罗贡，离他远点。去叫大家过来。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">呵呵…异形吗。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">有什么好笑的？</t>
-  </si>
-  <si>
-    <t xml:space="preserve">灾眼的「库罗茨亚」啊，汝还尚未察觉吗？汝体内蕴藏着古老的力量，那是能招致灾祸的古老的毁灭之力，汝亦为异形之一。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">你…你怎么知道我的事情…？</t>
-  </si>
-  <si>
-    <t xml:space="preserve">好疼！ 我知道了我知道了，小家伙，现在就过去，别拽我了…啊…你、你…你是谁啊？　</t>
-  </si>
-  <si>
-    <t xml:space="preserve">大伙都来了！</t>
-  </si>
-  <si>
-    <t xml:space="preserve">这个男人是…</t>
-  </si>
-  <si>
-    <t xml:space="preserve">嚯…传说中的龙，加上灾眼的魔女，还有「初代炼金术师」。呵呵，竟能全部聚集于此，让人有种置身于神话之中的感觉呢。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">等下，你认识这个家伙，凯特尔？</t>
-  </si>
-  <si>
-    <t xml:space="preserve">「凯特尔」…这就是你现在的名字吗。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">…大家不要担心。这个男人的名字是迪米塔斯，是「流放者」。他应该不会伤害我们。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">流放者…？</t>
-  </si>
-  <si>
-    <t xml:space="preserve">流放者是触及世界的禁忌，为了偿还自己的罪孽被神使役的可怜之人。而他，甚至被自己侍奉的神所抛弃。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">…汝还是一点没变。吾确实失去了自己的目的和存在的意义，只是四处徘徊而已。
-然而，呵呵……汝又是否找到那所谓的意义与目标呢？看来吾还太年轻，不足以理解那永恒的痛苦啊，「凯特尔」。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">我只是个随风漂泊的流浪炼金术师。可能会在旅途中找到自己的意义，也可能不会。
-迪米塔斯，能问问你造访这里的意图吗？</t>
-  </si>
-  <si>
-    <t xml:space="preserve">…有只自古潜藏在此的恶魔消失了。其名为特菲拉。
-吾不过是路过此处，顺道前来观察一番罢了。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">…不，不如说吾是被吸引而来的，飘荡在这片土地上的命运异味。被众神所抛弃的可怜、愚昧而又令人忌惮的孩童，将再度开启疯狂之宴。
-有趣，让吾暂且留于此处，静静观察一番吧。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">那个男人说的事情…</t>
-  </si>
-  <si>
-    <t xml:space="preserve">呜，在我脑海里挥之不去。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">我身体中沉睡的力量……</t>
-  </si>
-  <si>
-    <t xml:space="preserve">能招致灾祸的古老的毁灭之力</t>
-  </si>
-  <si>
-    <t xml:space="preserve">姆啾……</t>
-  </si>
-  <si>
-    <t xml:space="preserve">自从遇到凯特尔之后……不，应该说是自从和罗伊特尔他们一起生活开始，就很少做噩梦了。我也不需要去考虑自己到底是什么人了。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">但是……</t>
-  </si>
-  <si>
-    <t xml:space="preserve">歌罗贡，我…</t>
-  </si>
-  <si>
-    <t xml:space="preserve">睡不着吗，小姑娘。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">流放者迪米塔斯…</t>
-  </si>
-  <si>
-    <t xml:space="preserve">看起来汝还无法驾驭那眼中寄宿的力量。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">我的眼睛…你说什么？</t>
-  </si>
-  <si>
-    <t xml:space="preserve">呵呵…那光芒…赤红的灾厄之光，当它寄宿在汝的眼中，混沌将降临于世。灾眼之女，汝尚不知自身的宿命。然而，那时终将到来，正如那一日一般。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">…那天？</t>
-  </si>
-  <si>
-    <t xml:space="preserve">不懂吾之所指吗。汝应该还没忘记吧，汝村子里发生的惨剧。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">…为什么你会知道…我和你明明以前没见过。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">呵呵呵...是这样吗？
-连吾也是第一次见到如此诅咒。汝双眸中寄宿的赤色光芒，究竟是憎恨之焰，抑或是恍惚之光？
-一夜之间，汝之村落便…</t>
-  </si>
-  <si>
-    <t xml:space="preserve">住口！</t>
-  </si>
-  <si>
-    <t xml:space="preserve">那声音…不…竟让吾险些提起往昔之事…
-汝之力量…不错，吾等一直在密切关注着继承古老血脉的汝。
-少女啊，那一日，「凯特尔」救下汝之性命，汝以为那是巧合吗？</t>
-  </si>
-  <si>
-    <t xml:space="preserve">离我远点。我不想听你的话了。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">呵呵呵…汝实不知情。
-那人不过是利用尔等罢了。无论是救汝性命，还是如今让汝与龙相遇，一切不过是为了满足他的私欲而已。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">我才不相信呢。你讲的…全都是谎话！</t>
-  </si>
-  <si>
-    <t xml:space="preserve">姆啾！！</t>
-  </si>
-  <si>
-    <t xml:space="preserve">嚯…这只龙如此稚嫩…竟会回应愤怒之声，且能与人类心意如此相通，倒是有趣。
-钢铁龙的幼子…魔石…石之容器…
-呵呵呵，原来如此，事情竟是如此。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">夜已经深了。离去之前，再告诉汝一件事情吧，灾眼之女。
-那头幼龙「太小」了。它的成长被抑制了，或许是出于自身的意志，也可能遭到了某种外力。
-遗憾的告诉你，若如此下去，它恐怕活不长了</t>
-  </si>
-  <si>
-    <t xml:space="preserve">歌罗贡…？等下，你说的是什么意思！</t>
-  </si>
-  <si>
-    <t xml:space="preserve">去问「凯特尔」就好。看来，那个人向汝隐瞒了很多秘密…呵呵呵…</t>
-  </si>
 </sst>
 </file>
 
@@ -977,19 +741,19 @@
     <font>
       <sz val="10"/>
       <name val="Arial"/>
-      <family/>
+      <family val="0"/>
       <charset val="128"/>
     </font>
     <font>
       <sz val="10"/>
       <name val="Arial"/>
-      <family/>
+      <family val="0"/>
       <charset val="128"/>
     </font>
     <font>
       <sz val="10"/>
       <name val="Arial"/>
-      <family/>
+      <family val="0"/>
       <charset val="128"/>
     </font>
     <font>
@@ -1002,7 +766,7 @@
     <font>
       <sz val="11"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <family/>
+      <family val="0"/>
       <charset val="128"/>
     </font>
     <font>
@@ -1049,7 +813,7 @@
     </fill>
   </fills>
   <borders count="1">
-    <border>
+    <border diagonalUp="false" diagonalDown="false">
       <left/>
       <right/>
       <top/>
@@ -1058,98 +822,98 @@
     </border>
   </borders>
   <cellStyleXfs count="20">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment/>
-      <protection locked="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
   <cellXfs count="17">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="0">
-      <alignment/>
-      <protection locked="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyProtection="1">
-      <alignment/>
-      <protection locked="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment/>
-      <protection locked="1"/>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment wrapText="1"/>
-      <protection locked="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment/>
-      <protection locked="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment/>
-      <protection locked="1"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment/>
-      <protection locked="1"/>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment/>
-      <protection locked="1"/>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment wrapText="1"/>
-      <protection locked="1"/>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment wrapText="1"/>
-      <protection locked="1"/>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment wrapText="1"/>
-      <protection locked="1"/>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment wrapText="1"/>
-      <protection locked="1"/>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment wrapText="1"/>
-      <protection locked="1"/>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment wrapText="1"/>
-      <protection locked="1"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment wrapText="1"/>
-      <protection locked="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyProtection="1">
-      <alignment/>
-      <protection locked="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment/>
-      <protection locked="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -1163,13 +927,13 @@
   <dxfs count="1">
     <dxf>
       <font>
+        <name val="游ゴシック"/>
+        <charset val="128"/>
+        <family val="2"/>
         <color rgb="FFCC0000"/>
-        <name val="游ゴシック"/>
-        <family val="2"/>
-        <charset val="128"/>
       </font>
       <fill>
-        <patternFill patternType="solid">
+        <patternFill>
           <bgColor rgb="FFFFCCCC"/>
         </patternFill>
       </fill>
@@ -1345,26 +1109,26 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <sheetPr>
-    <pageSetUpPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:L148"/>
-  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col min="1" max="1" width="8.85" style="1" customWidth="1"/>
-    <col min="2" max="2" width="19.85" style="1" customWidth="1"/>
-    <col min="3" max="3" width="21.28" style="1" customWidth="1"/>
-    <col min="4" max="5" width="11.85" style="1" customWidth="1"/>
-    <col min="6" max="6" width="16.12" style="1" customWidth="1"/>
-    <col min="7" max="7" width="11.7" style="1" customWidth="1"/>
-    <col min="8" max="9" width="7.09" style="1" customWidth="1"/>
-    <col min="10" max="10" width="60.76" style="1" customWidth="1"/>
-    <col min="11" max="11" width="53.28" style="1" customWidth="1"/>
-    <col min="12" max="12" width="9.06" style="1" customWidth="1"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="8.85"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="19.85"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="21.28"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="4" style="1" width="11.85"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="16.12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="11.7"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="8" style="1" width="7.09"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="60.76"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="1" width="53.28"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="1" width="9.06"/>
   </cols>
   <sheetData>
-    <row r="1" ht="12.8">
+    <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1402,24 +1166,24 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" ht="12.8">
-      <c r="I2" s="1">
-        <f>MAX(I4:I1048576)</f>
+    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I2" s="1" t="n">
+        <f aca="false">MAX(I4:I1048576)</f>
         <v>82</v>
       </c>
     </row>
-    <row r="5" ht="12.8">
+    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B5" s="1" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="7" ht="12.8">
+    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="8" ht="12.8">
-      <c r="I8" s="1">
+    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I8" s="1" t="n">
         <v>1</v>
       </c>
       <c r="J8" s="3" t="s">
@@ -1428,15 +1192,12 @@
       <c r="K8" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="L8" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="9" ht="12.8">
+    </row>
+    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="J9" s="4"/>
       <c r="K9" s="4"/>
     </row>
-    <row r="10" ht="12.8">
+    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E10" s="1" t="s">
         <v>16</v>
       </c>
@@ -1444,22 +1205,22 @@
         <v>17</v>
       </c>
     </row>
-    <row r="11" ht="12.8">
+    <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E11" s="1" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="12" ht="12.8">
+    <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E12" s="1" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="15" ht="12.8">
+    <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="1" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="16" ht="12.8">
+    <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E16" s="1" t="s">
         <v>21</v>
       </c>
@@ -1467,7 +1228,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="17" ht="12.8">
+    <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E17" s="1" t="s">
         <v>23</v>
       </c>
@@ -1475,8 +1236,8 @@
         <v>24</v>
       </c>
     </row>
-    <row r="18" ht="13.8">
-      <c r="I18" s="1">
+    <row r="18" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I18" s="1" t="n">
         <v>2</v>
       </c>
       <c r="J18" s="6" t="s">
@@ -1485,15 +1246,12 @@
       <c r="K18" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="L18" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="19" ht="13.8">
+    </row>
+    <row r="19" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G19" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="I19" s="1">
+      <c r="I19" s="1" t="n">
         <v>3</v>
       </c>
       <c r="J19" s="7" t="s">
@@ -1502,12 +1260,9 @@
       <c r="K19" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="L19" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="20" ht="13.8">
-      <c r="I20" s="1">
+    </row>
+    <row r="20" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I20" s="1" t="n">
         <v>4</v>
       </c>
       <c r="J20" s="7" t="s">
@@ -1516,15 +1271,12 @@
       <c r="K20" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="L20" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="21" ht="13.8">
+    </row>
+    <row r="21" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G21" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="I21" s="1">
+      <c r="I21" s="1" t="n">
         <v>5</v>
       </c>
       <c r="J21" s="7" t="s">
@@ -1533,12 +1285,9 @@
       <c r="K21" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="L21" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="22" ht="13.8">
-      <c r="I22" s="1">
+    </row>
+    <row r="22" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I22" s="1" t="n">
         <v>6</v>
       </c>
       <c r="J22" s="7" t="s">
@@ -1547,15 +1296,12 @@
       <c r="K22" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="L22" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="23" ht="13.8">
+    </row>
+    <row r="23" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G23" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="I23" s="1">
+      <c r="I23" s="1" t="n">
         <v>7</v>
       </c>
       <c r="J23" s="7" t="s">
@@ -1564,12 +1310,9 @@
       <c r="K23" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="L23" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="24" ht="13.8">
-      <c r="I24" s="1">
+    </row>
+    <row r="24" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I24" s="1" t="n">
         <v>8</v>
       </c>
       <c r="J24" s="7" t="s">
@@ -1578,15 +1321,12 @@
       <c r="K24" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="L24" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="25" ht="13.8">
+    </row>
+    <row r="25" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G25" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="I25" s="1">
+      <c r="I25" s="1" t="n">
         <v>9</v>
       </c>
       <c r="J25" s="7" t="s">
@@ -1595,12 +1335,9 @@
       <c r="K25" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="L25" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="26" ht="13.8">
-      <c r="I26" s="1">
+    </row>
+    <row r="26" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I26" s="1" t="n">
         <v>10</v>
       </c>
       <c r="J26" s="7" t="s">
@@ -1609,15 +1346,12 @@
       <c r="K26" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="L26" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="27" ht="13.8">
+    </row>
+    <row r="27" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G27" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="I27" s="1">
+      <c r="I27" s="1" t="n">
         <v>11</v>
       </c>
       <c r="J27" s="7" t="s">
@@ -1626,12 +1360,9 @@
       <c r="K27" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="L27" t="s">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="28" ht="13.8">
-      <c r="I28" s="1">
+    </row>
+    <row r="28" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I28" s="1" t="n">
         <v>12</v>
       </c>
       <c r="J28" s="9" t="s">
@@ -1640,15 +1371,12 @@
       <c r="K28" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="L28" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="29" ht="22.35">
+    </row>
+    <row r="29" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G29" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="I29" s="1">
+      <c r="I29" s="1" t="n">
         <v>13</v>
       </c>
       <c r="J29" s="7" t="s">
@@ -1657,15 +1385,12 @@
       <c r="K29" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="L29" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="30" ht="43.25">
+    </row>
+    <row r="30" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G30" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="I30" s="1">
+      <c r="I30" s="1" t="n">
         <v>14</v>
       </c>
       <c r="J30" s="7" t="s">
@@ -1674,12 +1399,9 @@
       <c r="K30" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="L30" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="31" ht="13.8">
-      <c r="I31" s="1">
+    </row>
+    <row r="31" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I31" s="1" t="n">
         <v>15</v>
       </c>
       <c r="J31" s="10" t="s">
@@ -1688,15 +1410,12 @@
       <c r="K31" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="L31" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="32" ht="13.8">
+    </row>
+    <row r="32" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G32" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="I32" s="1">
+      <c r="I32" s="1" t="n">
         <v>16</v>
       </c>
       <c r="J32" s="7" t="s">
@@ -1705,12 +1424,9 @@
       <c r="K32" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="L32" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="33" ht="13.8">
-      <c r="I33" s="1">
+    </row>
+    <row r="33" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I33" s="1" t="n">
         <v>17</v>
       </c>
       <c r="J33" s="7" t="s">
@@ -1719,15 +1435,12 @@
       <c r="K33" s="11" t="s">
         <v>50</v>
       </c>
-      <c r="L33" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="34" ht="13.8">
+    </row>
+    <row r="34" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G34" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="I34" s="1">
+      <c r="I34" s="1" t="n">
         <v>18</v>
       </c>
       <c r="J34" s="6" t="s">
@@ -1736,15 +1449,12 @@
       <c r="K34" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="L34" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="35" ht="13.8">
+    </row>
+    <row r="35" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G35" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="I35" s="1">
+      <c r="I35" s="1" t="n">
         <v>19</v>
       </c>
       <c r="J35" s="6" t="s">
@@ -1753,15 +1463,12 @@
       <c r="K35" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="L35" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="36" ht="13.8">
+    </row>
+    <row r="36" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G36" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="I36" s="1">
+      <c r="I36" s="1" t="n">
         <v>20</v>
       </c>
       <c r="J36" s="6" t="s">
@@ -1770,24 +1477,21 @@
       <c r="K36" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="L36" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="37" ht="13.8">
+    </row>
+    <row r="37" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="J37" s="10"/>
     </row>
-    <row r="38" ht="12.8">
+    <row r="38" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E38" s="1" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="41" ht="12.8">
+    <row r="41" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E41" s="1" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="44" s="1" customFormat="1" ht="22.35">
+    <row r="44" s="1" customFormat="true" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="3" t="s">
         <v>57</v>
       </c>
@@ -1802,7 +1506,7 @@
       <c r="K44" s="3"/>
       <c r="L44" s="3"/>
     </row>
-    <row r="45" s="1" customFormat="1" ht="15.65">
+    <row r="45" s="1" customFormat="true" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="3"/>
       <c r="B45" s="3"/>
       <c r="C45" s="3"/>
@@ -1819,7 +1523,7 @@
       <c r="K45" s="3"/>
       <c r="L45" s="3"/>
     </row>
-    <row r="46" s="1" customFormat="1" ht="12.8">
+    <row r="46" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="3"/>
       <c r="B46" s="3"/>
       <c r="C46" s="3"/>
@@ -1836,7 +1540,7 @@
       <c r="K46" s="3"/>
       <c r="L46" s="3"/>
     </row>
-    <row r="47" s="1" customFormat="1" ht="12.8">
+    <row r="47" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="3"/>
       <c r="B47" s="3"/>
       <c r="C47" s="3"/>
@@ -1849,7 +1553,7 @@
       <c r="K47" s="3"/>
       <c r="L47" s="3"/>
     </row>
-    <row r="48" s="1" customFormat="1" ht="12.8">
+    <row r="48" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="3"/>
       <c r="B48" s="3"/>
       <c r="C48" s="3"/>
@@ -1866,7 +1570,7 @@
       <c r="K48" s="3"/>
       <c r="L48" s="3"/>
     </row>
-    <row r="49" s="1" customFormat="1" ht="12.8">
+    <row r="49" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="3"/>
       <c r="B49" s="3"/>
       <c r="C49" s="3"/>
@@ -1874,7 +1578,7 @@
       <c r="E49" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="F49" s="3">
+      <c r="F49" s="3" t="n">
         <v>2</v>
       </c>
       <c r="G49" s="3"/>
@@ -1883,7 +1587,7 @@
       <c r="K49" s="3"/>
       <c r="L49" s="3"/>
     </row>
-    <row r="50" s="1" customFormat="1" ht="12.8">
+    <row r="50" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="3"/>
       <c r="B50" s="3"/>
       <c r="C50" s="3"/>
@@ -1900,7 +1604,7 @@
       <c r="K50" s="3"/>
       <c r="L50" s="3"/>
     </row>
-    <row r="51" s="1" customFormat="1" ht="12.8">
+    <row r="51" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="3"/>
       <c r="B51" s="3"/>
       <c r="C51" s="3"/>
@@ -1908,7 +1612,7 @@
       <c r="E51" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="F51" s="15">
+      <c r="F51" s="15" t="n">
         <v>74</v>
       </c>
       <c r="G51" s="3"/>
@@ -1917,7 +1621,7 @@
       <c r="K51" s="3"/>
       <c r="L51" s="3"/>
     </row>
-    <row r="52" s="1" customFormat="1" ht="12.8">
+    <row r="52" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="3"/>
       <c r="B52" s="3"/>
       <c r="C52" s="3"/>
@@ -1925,7 +1629,7 @@
       <c r="E52" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="F52" s="3">
+      <c r="F52" s="3" t="n">
         <v>2</v>
       </c>
       <c r="G52" s="3"/>
@@ -1934,7 +1638,7 @@
       <c r="K52" s="3"/>
       <c r="L52" s="3"/>
     </row>
-    <row r="53" s="1" customFormat="1" ht="13.8">
+    <row r="53" s="1" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="3"/>
       <c r="B53" s="3"/>
       <c r="C53" s="3"/>
@@ -1943,7 +1647,7 @@
       <c r="F53" s="3"/>
       <c r="G53" s="3"/>
       <c r="H53" s="3"/>
-      <c r="I53" s="1">
+      <c r="I53" s="1" t="n">
         <v>21</v>
       </c>
       <c r="J53" s="10" t="s">
@@ -1952,11 +1656,9 @@
       <c r="K53" s="11" t="s">
         <v>68</v>
       </c>
-      <c r="L53" s="3" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="54" s="1" customFormat="1" ht="13.8">
+      <c r="L53" s="3"/>
+    </row>
+    <row r="54" s="1" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="3"/>
       <c r="B54" s="3"/>
       <c r="C54" s="3"/>
@@ -1967,7 +1669,7 @@
         <v>69</v>
       </c>
       <c r="H54" s="3"/>
-      <c r="I54" s="3">
+      <c r="I54" s="3" t="n">
         <v>22</v>
       </c>
       <c r="J54" s="9" t="s">
@@ -1976,11 +1678,9 @@
       <c r="K54" s="11" t="s">
         <v>71</v>
       </c>
-      <c r="L54" s="3" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="55" s="1" customFormat="1" ht="13.8">
+      <c r="L54" s="3"/>
+    </row>
+    <row r="55" s="1" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="3"/>
       <c r="B55" s="3"/>
       <c r="C55" s="3"/>
@@ -1989,7 +1689,7 @@
       <c r="F55" s="3"/>
       <c r="G55" s="3"/>
       <c r="H55" s="3"/>
-      <c r="I55" s="1">
+      <c r="I55" s="1" t="n">
         <v>23</v>
       </c>
       <c r="J55" s="9" t="s">
@@ -1998,11 +1698,9 @@
       <c r="K55" s="11" t="s">
         <v>73</v>
       </c>
-      <c r="L55" s="3" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="56" s="1" customFormat="1" ht="13.8">
+      <c r="L55" s="3"/>
+    </row>
+    <row r="56" s="1" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="3"/>
       <c r="B56" s="3"/>
       <c r="C56" s="3"/>
@@ -2013,7 +1711,7 @@
         <v>69</v>
       </c>
       <c r="H56" s="3"/>
-      <c r="I56" s="1">
+      <c r="I56" s="1" t="n">
         <v>24</v>
       </c>
       <c r="J56" s="9" t="s">
@@ -2022,11 +1720,9 @@
       <c r="K56" s="11" t="s">
         <v>75</v>
       </c>
-      <c r="L56" s="3" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="57" s="1" customFormat="1" ht="13.8">
+      <c r="L56" s="3"/>
+    </row>
+    <row r="57" s="1" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="3"/>
       <c r="B57" s="3"/>
       <c r="C57" s="3"/>
@@ -2035,7 +1731,7 @@
       <c r="F57" s="3"/>
       <c r="G57" s="3"/>
       <c r="H57" s="3"/>
-      <c r="I57" s="1">
+      <c r="I57" s="1" t="n">
         <v>25</v>
       </c>
       <c r="J57" s="9" t="s">
@@ -2044,11 +1740,9 @@
       <c r="K57" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="L57" s="3" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="58" s="1" customFormat="1" ht="13.8">
+      <c r="L57" s="3"/>
+    </row>
+    <row r="58" s="1" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="3"/>
       <c r="B58" s="3"/>
       <c r="C58" s="3"/>
@@ -2059,7 +1753,7 @@
         <v>69</v>
       </c>
       <c r="H58" s="3"/>
-      <c r="I58" s="1">
+      <c r="I58" s="1" t="n">
         <v>26</v>
       </c>
       <c r="J58" s="9" t="s">
@@ -2068,11 +1762,9 @@
       <c r="K58" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="L58" s="3" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="59" s="1" customFormat="1" ht="13.8">
+      <c r="L58" s="3"/>
+    </row>
+    <row r="59" s="1" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="3"/>
       <c r="B59" s="3"/>
       <c r="C59" s="3"/>
@@ -2081,7 +1773,7 @@
       <c r="F59" s="3"/>
       <c r="G59" s="3"/>
       <c r="H59" s="3"/>
-      <c r="I59" s="1">
+      <c r="I59" s="1" t="n">
         <v>27</v>
       </c>
       <c r="J59" s="10" t="s">
@@ -2090,11 +1782,9 @@
       <c r="K59" s="11" t="s">
         <v>77</v>
       </c>
-      <c r="L59" s="3" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="60" s="1" customFormat="1" ht="13.8">
+      <c r="L59" s="3"/>
+    </row>
+    <row r="60" s="1" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="3"/>
       <c r="B60" s="3"/>
       <c r="C60" s="3"/>
@@ -2105,7 +1795,7 @@
         <v>69</v>
       </c>
       <c r="H60" s="3"/>
-      <c r="I60" s="1">
+      <c r="I60" s="1" t="n">
         <v>28</v>
       </c>
       <c r="J60" s="10" t="s">
@@ -2114,11 +1804,9 @@
       <c r="K60" s="11" t="s">
         <v>79</v>
       </c>
-      <c r="L60" s="3" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="61" s="1" customFormat="1" ht="13.8">
+      <c r="L60" s="3"/>
+    </row>
+    <row r="61" s="1" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="3"/>
       <c r="B61" s="3"/>
       <c r="C61" s="3"/>
@@ -2127,7 +1815,7 @@
       <c r="F61" s="3"/>
       <c r="G61" s="3"/>
       <c r="H61" s="3"/>
-      <c r="I61" s="1">
+      <c r="I61" s="1" t="n">
         <v>29</v>
       </c>
       <c r="J61" s="9" t="s">
@@ -2136,11 +1824,9 @@
       <c r="K61" s="11" t="s">
         <v>81</v>
       </c>
-      <c r="L61" s="3" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="62" s="1" customFormat="1" ht="13.8">
+      <c r="L61" s="3"/>
+    </row>
+    <row r="62" s="1" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="3"/>
       <c r="B62" s="3"/>
       <c r="C62" s="3"/>
@@ -2148,7 +1834,7 @@
       <c r="E62" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="F62" s="16">
+      <c r="F62" s="16" t="n">
         <v>3</v>
       </c>
       <c r="G62" s="3"/>
@@ -2157,7 +1843,7 @@
       <c r="K62" s="3"/>
       <c r="L62" s="3"/>
     </row>
-    <row r="63" s="1" customFormat="1" ht="13.8">
+    <row r="63" s="1" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="3"/>
       <c r="B63" s="3"/>
       <c r="C63" s="3"/>
@@ -2166,7 +1852,7 @@
       <c r="F63" s="3"/>
       <c r="G63" s="3"/>
       <c r="H63" s="3"/>
-      <c r="I63" s="1">
+      <c r="I63" s="1" t="n">
         <v>30</v>
       </c>
       <c r="J63" s="9" t="s">
@@ -2175,11 +1861,9 @@
       <c r="K63" s="11" t="s">
         <v>83</v>
       </c>
-      <c r="L63" s="3" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="64" s="1" customFormat="1" ht="13.8">
+      <c r="L63" s="3"/>
+    </row>
+    <row r="64" s="1" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="3"/>
       <c r="B64" s="3"/>
       <c r="C64" s="3"/>
@@ -2188,7 +1872,7 @@
       <c r="F64" s="3"/>
       <c r="G64" s="3"/>
       <c r="H64" s="3"/>
-      <c r="I64" s="1">
+      <c r="I64" s="1" t="n">
         <v>31</v>
       </c>
       <c r="J64" s="9" t="s">
@@ -2197,11 +1881,9 @@
       <c r="K64" s="11" t="s">
         <v>85</v>
       </c>
-      <c r="L64" s="3" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="65" s="1" customFormat="1" ht="13.8">
+      <c r="L64" s="3"/>
+    </row>
+    <row r="65" s="1" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="3"/>
       <c r="B65" s="3"/>
       <c r="C65" s="3"/>
@@ -2209,7 +1891,7 @@
       <c r="E65" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="F65" s="3">
+      <c r="F65" s="3" t="n">
         <v>1</v>
       </c>
       <c r="G65" s="3"/>
@@ -2218,7 +1900,7 @@
       <c r="K65" s="3"/>
       <c r="L65" s="3"/>
     </row>
-    <row r="66" s="1" customFormat="1" ht="13.8">
+    <row r="66" s="1" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="3"/>
       <c r="B66" s="3"/>
       <c r="C66" s="3"/>
@@ -2226,7 +1908,7 @@
       <c r="E66" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="F66" s="3">
+      <c r="F66" s="3" t="n">
         <v>1</v>
       </c>
       <c r="G66" s="3"/>
@@ -2235,7 +1917,7 @@
       <c r="K66" s="3"/>
       <c r="L66" s="3"/>
     </row>
-    <row r="67" s="1" customFormat="1" ht="13.8">
+    <row r="67" s="1" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="3"/>
       <c r="B67" s="3"/>
       <c r="C67" s="3"/>
@@ -2244,7 +1926,7 @@
       <c r="F67" s="3"/>
       <c r="G67" s="3"/>
       <c r="H67" s="3"/>
-      <c r="I67" s="1">
+      <c r="I67" s="1" t="n">
         <v>32</v>
       </c>
       <c r="J67" s="9" t="s">
@@ -2253,11 +1935,9 @@
       <c r="K67" s="11" t="s">
         <v>87</v>
       </c>
-      <c r="L67" s="3" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="68" s="1" customFormat="1" ht="13.8">
+      <c r="L67" s="3"/>
+    </row>
+    <row r="68" s="1" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="3"/>
       <c r="B68" s="3"/>
       <c r="C68" s="3"/>
@@ -2274,7 +1954,7 @@
       <c r="K68" s="3"/>
       <c r="L68" s="3"/>
     </row>
-    <row r="69" s="1" customFormat="1" ht="15.65">
+    <row r="69" s="1" customFormat="true" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="3"/>
       <c r="B69" s="3"/>
       <c r="C69" s="3"/>
@@ -2285,7 +1965,7 @@
         <v>58</v>
       </c>
       <c r="H69" s="3"/>
-      <c r="I69" s="1">
+      <c r="I69" s="1" t="n">
         <v>33</v>
       </c>
       <c r="J69" s="9" t="s">
@@ -2294,11 +1974,9 @@
       <c r="K69" s="11" t="s">
         <v>90</v>
       </c>
-      <c r="L69" s="3" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="70" s="1" customFormat="1" ht="13.8">
+      <c r="L69" s="3"/>
+    </row>
+    <row r="70" s="1" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="3"/>
       <c r="B70" s="3"/>
       <c r="C70" s="3"/>
@@ -2309,7 +1987,7 @@
         <v>69</v>
       </c>
       <c r="H70" s="3"/>
-      <c r="I70" s="1">
+      <c r="I70" s="1" t="n">
         <v>34</v>
       </c>
       <c r="J70" s="9" t="s">
@@ -2318,11 +1996,9 @@
       <c r="K70" s="11" t="s">
         <v>92</v>
       </c>
-      <c r="L70" s="3" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="71" s="1" customFormat="1" ht="15.65">
+      <c r="L70" s="3"/>
+    </row>
+    <row r="71" s="1" customFormat="true" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="3"/>
       <c r="B71" s="3"/>
       <c r="C71" s="3"/>
@@ -2333,7 +2009,7 @@
         <v>58</v>
       </c>
       <c r="H71" s="3"/>
-      <c r="I71" s="1">
+      <c r="I71" s="1" t="n">
         <v>35</v>
       </c>
       <c r="J71" s="9" t="s">
@@ -2342,11 +2018,9 @@
       <c r="K71" s="11" t="s">
         <v>94</v>
       </c>
-      <c r="L71" s="3" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="72" s="1" customFormat="1" ht="43.25">
+      <c r="L71" s="3"/>
+    </row>
+    <row r="72" s="1" customFormat="true" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="3"/>
       <c r="B72" s="3"/>
       <c r="C72" s="3"/>
@@ -2355,7 +2029,7 @@
       <c r="F72" s="3"/>
       <c r="G72" s="3"/>
       <c r="H72" s="3"/>
-      <c r="I72" s="1">
+      <c r="I72" s="1" t="n">
         <v>36</v>
       </c>
       <c r="J72" s="9" t="s">
@@ -2364,11 +2038,9 @@
       <c r="K72" s="3" t="s">
         <v>96</v>
       </c>
-      <c r="L72" s="3" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="73" s="1" customFormat="1" ht="15.65">
+      <c r="L72" s="3"/>
+    </row>
+    <row r="73" s="1" customFormat="true" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="3"/>
       <c r="B73" s="3"/>
       <c r="C73" s="3"/>
@@ -2379,7 +2051,7 @@
         <v>58</v>
       </c>
       <c r="H73" s="3"/>
-      <c r="I73" s="1">
+      <c r="I73" s="1" t="n">
         <v>37</v>
       </c>
       <c r="J73" s="9" t="s">
@@ -2388,11 +2060,9 @@
       <c r="K73" s="11" t="s">
         <v>98</v>
       </c>
-      <c r="L73" s="3" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="74" s="1" customFormat="1" ht="13.8">
+      <c r="L73" s="3"/>
+    </row>
+    <row r="74" s="1" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="3"/>
       <c r="B74" s="3"/>
       <c r="C74" s="3"/>
@@ -2401,7 +2071,7 @@
       <c r="F74" s="3"/>
       <c r="G74" s="3"/>
       <c r="H74" s="3"/>
-      <c r="I74" s="1">
+      <c r="I74" s="1" t="n">
         <v>38</v>
       </c>
       <c r="J74" s="9" t="s">
@@ -2410,11 +2080,9 @@
       <c r="K74" s="11" t="s">
         <v>100</v>
       </c>
-      <c r="L74" s="3" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="75" s="1" customFormat="1" ht="37.3">
+      <c r="L74" s="3"/>
+    </row>
+    <row r="75" s="1" customFormat="true" ht="37.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="3"/>
       <c r="B75" s="3"/>
       <c r="C75" s="3"/>
@@ -2425,7 +2093,7 @@
         <v>58</v>
       </c>
       <c r="H75" s="3"/>
-      <c r="I75" s="1">
+      <c r="I75" s="1" t="n">
         <v>39</v>
       </c>
       <c r="J75" s="9" t="s">
@@ -2434,11 +2102,9 @@
       <c r="K75" s="11" t="s">
         <v>102</v>
       </c>
-      <c r="L75" s="3" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="76" s="1" customFormat="1" ht="13.8">
+      <c r="L75" s="3"/>
+    </row>
+    <row r="76" s="1" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="3"/>
       <c r="B76" s="3"/>
       <c r="C76" s="3"/>
@@ -2447,7 +2113,7 @@
       <c r="F76" s="3"/>
       <c r="G76" s="3"/>
       <c r="H76" s="3"/>
-      <c r="I76" s="1">
+      <c r="I76" s="1" t="n">
         <v>40</v>
       </c>
       <c r="J76" s="9" t="s">
@@ -2456,11 +2122,9 @@
       <c r="K76" s="11" t="s">
         <v>104</v>
       </c>
-      <c r="L76" s="3" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="77" s="1" customFormat="1" ht="25.35">
+      <c r="L76" s="3"/>
+    </row>
+    <row r="77" s="1" customFormat="true" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="3"/>
       <c r="B77" s="3"/>
       <c r="C77" s="3"/>
@@ -2471,7 +2135,7 @@
         <v>22</v>
       </c>
       <c r="H77" s="3"/>
-      <c r="I77" s="1">
+      <c r="I77" s="1" t="n">
         <v>41</v>
       </c>
       <c r="J77" s="9" t="s">
@@ -2480,11 +2144,9 @@
       <c r="K77" s="11" t="s">
         <v>106</v>
       </c>
-      <c r="L77" s="3" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="78" s="1" customFormat="1" ht="13.8">
+      <c r="L77" s="3"/>
+    </row>
+    <row r="78" s="1" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="3"/>
       <c r="B78" s="3"/>
       <c r="C78" s="3"/>
@@ -2493,7 +2155,7 @@
       <c r="F78" s="3"/>
       <c r="G78" s="3"/>
       <c r="H78" s="3"/>
-      <c r="I78" s="1">
+      <c r="I78" s="1" t="n">
         <v>42</v>
       </c>
       <c r="J78" s="9" t="s">
@@ -2502,11 +2164,9 @@
       <c r="K78" s="11" t="s">
         <v>108</v>
       </c>
-      <c r="L78" s="3" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="79" s="1" customFormat="1" ht="13.8">
+      <c r="L78" s="3"/>
+    </row>
+    <row r="79" s="1" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="3"/>
       <c r="B79" s="3"/>
       <c r="C79" s="3"/>
@@ -2517,7 +2177,7 @@
         <v>109</v>
       </c>
       <c r="H79" s="3"/>
-      <c r="I79" s="1">
+      <c r="I79" s="1" t="n">
         <v>43</v>
       </c>
       <c r="J79" s="9" t="s">
@@ -2526,11 +2186,9 @@
       <c r="K79" s="11" t="s">
         <v>111</v>
       </c>
-      <c r="L79" s="3" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="80" s="1" customFormat="1" ht="13.8">
+      <c r="L79" s="3"/>
+    </row>
+    <row r="80" s="1" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="3"/>
       <c r="B80" s="3"/>
       <c r="C80" s="3"/>
@@ -2543,7 +2201,7 @@
       <c r="K80" s="3"/>
       <c r="L80" s="3"/>
     </row>
-    <row r="81" s="1" customFormat="1" ht="25.35">
+    <row r="81" s="1" customFormat="true" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="3"/>
       <c r="B81" s="3"/>
       <c r="C81" s="3"/>
@@ -2554,7 +2212,7 @@
         <v>58</v>
       </c>
       <c r="H81" s="3"/>
-      <c r="I81" s="1">
+      <c r="I81" s="1" t="n">
         <v>44</v>
       </c>
       <c r="J81" s="9" t="s">
@@ -2563,11 +2221,9 @@
       <c r="K81" s="11" t="s">
         <v>113</v>
       </c>
-      <c r="L81" s="3" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="82" s="1" customFormat="1" ht="13.8">
+      <c r="L81" s="3"/>
+    </row>
+    <row r="82" s="1" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="3"/>
       <c r="B82" s="3"/>
       <c r="C82" s="3"/>
@@ -2578,7 +2234,7 @@
         <v>22</v>
       </c>
       <c r="H82" s="3"/>
-      <c r="I82" s="1">
+      <c r="I82" s="1" t="n">
         <v>45</v>
       </c>
       <c r="J82" s="10" t="s">
@@ -2587,11 +2243,9 @@
       <c r="K82" s="11" t="s">
         <v>115</v>
       </c>
-      <c r="L82" s="3" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="83" s="1" customFormat="1" ht="15.65">
+      <c r="L82" s="3"/>
+    </row>
+    <row r="83" s="1" customFormat="true" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A83" s="3"/>
       <c r="B83" s="3"/>
       <c r="C83" s="3"/>
@@ -2602,7 +2256,7 @@
         <v>58</v>
       </c>
       <c r="H83" s="3"/>
-      <c r="I83" s="1">
+      <c r="I83" s="1" t="n">
         <v>46</v>
       </c>
       <c r="J83" s="9" t="s">
@@ -2611,11 +2265,9 @@
       <c r="K83" s="11" t="s">
         <v>117</v>
       </c>
-      <c r="L83" s="3" t="s">
-        <v>231</v>
-      </c>
-    </row>
-    <row r="84" s="1" customFormat="1" ht="23.85">
+      <c r="L83" s="3"/>
+    </row>
+    <row r="84" s="1" customFormat="true" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A84" s="3"/>
       <c r="B84" s="3"/>
       <c r="C84" s="3"/>
@@ -2626,7 +2278,7 @@
         <v>109</v>
       </c>
       <c r="H84" s="3"/>
-      <c r="I84" s="1">
+      <c r="I84" s="1" t="n">
         <v>47</v>
       </c>
       <c r="J84" s="10" t="s">
@@ -2635,11 +2287,9 @@
       <c r="K84" s="11" t="s">
         <v>119</v>
       </c>
-      <c r="L84" s="3" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="85" s="1" customFormat="1" ht="13.8">
+      <c r="L84" s="3"/>
+    </row>
+    <row r="85" s="1" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A85" s="3"/>
       <c r="B85" s="3"/>
       <c r="C85" s="3"/>
@@ -2648,7 +2298,7 @@
       <c r="F85" s="3"/>
       <c r="G85" s="12"/>
       <c r="H85" s="3"/>
-      <c r="I85" s="1">
+      <c r="I85" s="1" t="n">
         <v>48</v>
       </c>
       <c r="J85" s="9" t="s">
@@ -2657,11 +2307,9 @@
       <c r="K85" s="11" t="s">
         <v>121</v>
       </c>
-      <c r="L85" s="3" t="s">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="86" s="1" customFormat="1" ht="37.3">
+      <c r="L85" s="3"/>
+    </row>
+    <row r="86" s="1" customFormat="true" ht="37.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A86" s="3"/>
       <c r="B86" s="3"/>
       <c r="C86" s="3"/>
@@ -2672,7 +2320,7 @@
         <v>109</v>
       </c>
       <c r="H86" s="3"/>
-      <c r="I86" s="1">
+      <c r="I86" s="1" t="n">
         <v>49</v>
       </c>
       <c r="J86" s="9" t="s">
@@ -2681,11 +2329,9 @@
       <c r="K86" s="11" t="s">
         <v>123</v>
       </c>
-      <c r="L86" s="3" t="s">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="87" s="1" customFormat="1" ht="64.15">
+      <c r="L86" s="3"/>
+    </row>
+    <row r="87" s="1" customFormat="true" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A87" s="3"/>
       <c r="B87" s="3"/>
       <c r="C87" s="3"/>
@@ -2696,7 +2342,7 @@
         <v>124</v>
       </c>
       <c r="H87" s="3"/>
-      <c r="I87" s="1">
+      <c r="I87" s="1" t="n">
         <v>50</v>
       </c>
       <c r="J87" s="10" t="s">
@@ -2705,11 +2351,9 @@
       <c r="K87" s="3" t="s">
         <v>126</v>
       </c>
-      <c r="L87" s="3" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="88" s="1" customFormat="1" ht="46.25">
+      <c r="L87" s="3"/>
+    </row>
+    <row r="88" s="1" customFormat="true" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A88" s="3"/>
       <c r="B88" s="3"/>
       <c r="C88" s="3"/>
@@ -2720,7 +2364,7 @@
         <v>109</v>
       </c>
       <c r="H88" s="3"/>
-      <c r="I88" s="1">
+      <c r="I88" s="1" t="n">
         <v>51</v>
       </c>
       <c r="J88" s="10" t="s">
@@ -2729,11 +2373,9 @@
       <c r="K88" s="3" t="s">
         <v>128</v>
       </c>
-      <c r="L88" s="3" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="89" s="1" customFormat="1" ht="46.25">
+      <c r="L88" s="3"/>
+    </row>
+    <row r="89" s="1" customFormat="true" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A89" s="3"/>
       <c r="B89" s="3"/>
       <c r="C89" s="3"/>
@@ -2744,7 +2386,7 @@
         <v>124</v>
       </c>
       <c r="H89" s="3"/>
-      <c r="I89" s="1">
+      <c r="I89" s="1" t="n">
         <v>52</v>
       </c>
       <c r="J89" s="10" t="s">
@@ -2753,11 +2395,9 @@
       <c r="K89" s="3" t="s">
         <v>130</v>
       </c>
-      <c r="L89" s="3" t="s">
-        <v>237</v>
-      </c>
-    </row>
-    <row r="90" s="1" customFormat="1" ht="68.65">
+      <c r="L89" s="3"/>
+    </row>
+    <row r="90" s="1" customFormat="true" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A90" s="3"/>
       <c r="B90" s="3"/>
       <c r="C90" s="3"/>
@@ -2768,7 +2408,7 @@
         <v>124</v>
       </c>
       <c r="H90" s="3"/>
-      <c r="I90" s="1">
+      <c r="I90" s="1" t="n">
         <v>53</v>
       </c>
       <c r="J90" s="10" t="s">
@@ -2777,11 +2417,9 @@
       <c r="K90" s="3" t="s">
         <v>132</v>
       </c>
-      <c r="L90" s="3" t="s">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="91" s="1" customFormat="1" ht="22.35">
+      <c r="L90" s="3"/>
+    </row>
+    <row r="91" s="1" customFormat="true" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A91" s="3"/>
       <c r="B91" s="3"/>
       <c r="C91" s="3"/>
@@ -2796,7 +2434,7 @@
       <c r="K91" s="3"/>
       <c r="L91" s="3"/>
     </row>
-    <row r="92" s="1" customFormat="1" ht="12.8">
+    <row r="92" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A92" s="3"/>
       <c r="B92" s="3"/>
       <c r="C92" s="3"/>
@@ -2809,7 +2447,7 @@
       <c r="K92" s="3"/>
       <c r="L92" s="3"/>
     </row>
-    <row r="93" s="1" customFormat="1" ht="12.8">
+    <row r="93" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A93" s="3"/>
       <c r="B93" s="3"/>
       <c r="C93" s="3"/>
@@ -2817,7 +2455,7 @@
       <c r="E93" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="F93" s="14">
+      <c r="F93" s="14" t="n">
         <v>3</v>
       </c>
       <c r="G93" s="3"/>
@@ -2826,7 +2464,7 @@
       <c r="K93" s="3"/>
       <c r="L93" s="3"/>
     </row>
-    <row r="94" s="1" customFormat="1" ht="12.8">
+    <row r="94" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A94" s="3"/>
       <c r="B94" s="3"/>
       <c r="C94" s="3"/>
@@ -2841,7 +2479,7 @@
       <c r="K94" s="3"/>
       <c r="L94" s="3"/>
     </row>
-    <row r="95" s="1" customFormat="1" ht="12.8">
+    <row r="95" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A95" s="3"/>
       <c r="B95" s="3"/>
       <c r="C95" s="3"/>
@@ -2854,7 +2492,7 @@
       <c r="K95" s="3"/>
       <c r="L95" s="3"/>
     </row>
-    <row r="97" s="1" customFormat="1" ht="22.35">
+    <row r="97" s="1" customFormat="true" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A97" s="3" t="s">
         <v>133</v>
       </c>
@@ -2869,7 +2507,7 @@
       <c r="K97" s="3"/>
       <c r="L97" s="3"/>
     </row>
-    <row r="98" s="1" customFormat="1" ht="12.8">
+    <row r="98" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A98" s="3"/>
       <c r="B98" s="3"/>
       <c r="C98" s="3"/>
@@ -2886,7 +2524,7 @@
       <c r="K98" s="3"/>
       <c r="L98" s="3"/>
     </row>
-    <row r="99" ht="12.8">
+    <row r="99" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A99" s="3"/>
       <c r="B99" s="3"/>
       <c r="C99" s="3"/>
@@ -2903,7 +2541,7 @@
       <c r="K99" s="3"/>
       <c r="L99" s="3"/>
     </row>
-    <row r="100" ht="12.8">
+    <row r="100" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A100" s="3"/>
       <c r="B100" s="3"/>
       <c r="C100" s="3"/>
@@ -2911,7 +2549,7 @@
       <c r="E100" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="F100" s="3">
+      <c r="F100" s="3" t="n">
         <v>2</v>
       </c>
       <c r="G100" s="3"/>
@@ -2920,7 +2558,7 @@
       <c r="K100" s="3"/>
       <c r="L100" s="3"/>
     </row>
-    <row r="101" ht="12.8">
+    <row r="101" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A101" s="3"/>
       <c r="B101" s="3"/>
       <c r="C101" s="3"/>
@@ -2937,7 +2575,7 @@
       <c r="K101" s="3"/>
       <c r="L101" s="3"/>
     </row>
-    <row r="102" ht="12.8">
+    <row r="102" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A102" s="3"/>
       <c r="B102" s="3"/>
       <c r="C102" s="3"/>
@@ -2950,7 +2588,7 @@
       <c r="K102" s="3"/>
       <c r="L102" s="3"/>
     </row>
-    <row r="103" ht="12.8">
+    <row r="103" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A103" s="3"/>
       <c r="B103" s="3"/>
       <c r="C103" s="3"/>
@@ -2958,7 +2596,7 @@
       <c r="E103" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="F103" s="3">
+      <c r="F103" s="3" t="n">
         <v>2</v>
       </c>
       <c r="G103" s="3"/>
@@ -2967,7 +2605,7 @@
       <c r="K103" s="3"/>
       <c r="L103" s="3"/>
     </row>
-    <row r="104" s="1" customFormat="1" ht="12.8">
+    <row r="104" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A104" s="3"/>
       <c r="B104" s="3"/>
       <c r="C104" s="3"/>
@@ -2980,7 +2618,7 @@
       <c r="K104" s="3"/>
       <c r="L104" s="3"/>
     </row>
-    <row r="105" s="1" customFormat="1" ht="12.8">
+    <row r="105" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A105" s="3"/>
       <c r="B105" s="3"/>
       <c r="C105" s="3"/>
@@ -2993,7 +2631,7 @@
       <c r="K105" s="3"/>
       <c r="L105" s="3"/>
     </row>
-    <row r="106" s="1" customFormat="1" ht="12.8">
+    <row r="106" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A106" s="3"/>
       <c r="B106" s="3"/>
       <c r="C106" s="3"/>
@@ -3006,7 +2644,7 @@
       <c r="K106" s="3"/>
       <c r="L106" s="3"/>
     </row>
-    <row r="107" s="1" customFormat="1" ht="12.8">
+    <row r="107" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A107" s="3"/>
       <c r="B107" s="3"/>
       <c r="C107" s="3"/>
@@ -3019,7 +2657,7 @@
       <c r="K107" s="3"/>
       <c r="L107" s="3"/>
     </row>
-    <row r="108" s="1" customFormat="1" ht="12.8">
+    <row r="108" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A108" s="3"/>
       <c r="B108" s="3"/>
       <c r="C108" s="3"/>
@@ -3028,7 +2666,7 @@
       <c r="F108" s="3"/>
       <c r="G108" s="3"/>
       <c r="H108" s="3"/>
-      <c r="I108" s="1">
+      <c r="I108" s="1" t="n">
         <v>54</v>
       </c>
       <c r="J108" s="3" t="s">
@@ -3037,11 +2675,9 @@
       <c r="K108" s="11" t="s">
         <v>136</v>
       </c>
-      <c r="L108" s="3" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="109" s="1" customFormat="1" ht="12.8">
+      <c r="L108" s="3"/>
+    </row>
+    <row r="109" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A109" s="3"/>
       <c r="B109" s="3"/>
       <c r="C109" s="3"/>
@@ -3050,7 +2686,7 @@
       <c r="F109" s="3"/>
       <c r="G109" s="3"/>
       <c r="H109" s="3"/>
-      <c r="I109" s="1">
+      <c r="I109" s="1" t="n">
         <v>55</v>
       </c>
       <c r="J109" s="3" t="s">
@@ -3059,11 +2695,9 @@
       <c r="K109" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="L109" s="3" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="110" s="1" customFormat="1" ht="12.8">
+      <c r="L109" s="3"/>
+    </row>
+    <row r="110" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A110" s="3"/>
       <c r="B110" s="3"/>
       <c r="C110" s="3"/>
@@ -3072,7 +2706,7 @@
       <c r="F110" s="3"/>
       <c r="G110" s="3"/>
       <c r="H110" s="3"/>
-      <c r="I110" s="1">
+      <c r="I110" s="1" t="n">
         <v>56</v>
       </c>
       <c r="J110" s="3" t="s">
@@ -3081,11 +2715,9 @@
       <c r="K110" s="11" t="s">
         <v>138</v>
       </c>
-      <c r="L110" s="3" t="s">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="111" s="1" customFormat="1" ht="12.8">
+      <c r="L110" s="3"/>
+    </row>
+    <row r="111" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A111" s="3"/>
       <c r="B111" s="3"/>
       <c r="C111" s="3"/>
@@ -3102,7 +2734,7 @@
       <c r="K111" s="3"/>
       <c r="L111" s="3"/>
     </row>
-    <row r="112" s="1" customFormat="1" ht="13.8">
+    <row r="112" s="1" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A112" s="3"/>
       <c r="B112" s="3"/>
       <c r="C112" s="3"/>
@@ -3111,7 +2743,7 @@
       <c r="F112" s="14"/>
       <c r="G112" s="3"/>
       <c r="H112" s="3"/>
-      <c r="I112" s="1">
+      <c r="I112" s="1" t="n">
         <v>57</v>
       </c>
       <c r="J112" s="9" t="s">
@@ -3120,11 +2752,9 @@
       <c r="K112" s="11" t="s">
         <v>141</v>
       </c>
-      <c r="L112" s="3" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="113" s="1" customFormat="1" ht="13.8">
+      <c r="L112" s="3"/>
+    </row>
+    <row r="113" s="1" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A113" s="3"/>
       <c r="B113" s="3"/>
       <c r="C113" s="3"/>
@@ -3133,7 +2763,7 @@
       <c r="F113" s="3"/>
       <c r="G113" s="3"/>
       <c r="H113" s="3"/>
-      <c r="I113" s="1">
+      <c r="I113" s="1" t="n">
         <v>58</v>
       </c>
       <c r="J113" s="9" t="s">
@@ -3142,11 +2772,9 @@
       <c r="K113" s="11" t="s">
         <v>143</v>
       </c>
-      <c r="L113" s="3" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="114" s="1" customFormat="1" ht="13.8">
+      <c r="L113" s="3"/>
+    </row>
+    <row r="114" s="1" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A114" s="3"/>
       <c r="B114" s="3"/>
       <c r="C114" s="3"/>
@@ -3157,7 +2785,7 @@
         <v>69</v>
       </c>
       <c r="H114" s="3"/>
-      <c r="I114" s="1">
+      <c r="I114" s="1" t="n">
         <v>59</v>
       </c>
       <c r="J114" s="9" t="s">
@@ -3166,11 +2794,9 @@
       <c r="K114" s="11" t="s">
         <v>145</v>
       </c>
-      <c r="L114" s="3" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="115" s="1" customFormat="1" ht="37.3">
+      <c r="L114" s="3"/>
+    </row>
+    <row r="115" s="1" customFormat="true" ht="37.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A115" s="3"/>
       <c r="B115" s="3"/>
       <c r="C115" s="3"/>
@@ -3179,7 +2805,7 @@
       <c r="F115" s="3"/>
       <c r="G115" s="3"/>
       <c r="H115" s="3"/>
-      <c r="I115" s="1">
+      <c r="I115" s="1" t="n">
         <v>60</v>
       </c>
       <c r="J115" s="9" t="s">
@@ -3188,11 +2814,9 @@
       <c r="K115" s="11" t="s">
         <v>147</v>
       </c>
-      <c r="L115" s="3" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="116" s="1" customFormat="1" ht="13.8">
+      <c r="L115" s="3"/>
+    </row>
+    <row r="116" s="1" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A116" s="3"/>
       <c r="B116" s="3"/>
       <c r="C116" s="3"/>
@@ -3201,7 +2825,7 @@
       <c r="F116" s="3"/>
       <c r="G116" s="3"/>
       <c r="H116" s="3"/>
-      <c r="I116" s="1">
+      <c r="I116" s="1" t="n">
         <v>61</v>
       </c>
       <c r="J116" s="9" t="s">
@@ -3210,11 +2834,9 @@
       <c r="K116" s="11" t="s">
         <v>149</v>
       </c>
-      <c r="L116" s="3" t="s">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="117" s="1" customFormat="1" ht="13.8">
+      <c r="L116" s="3"/>
+    </row>
+    <row r="117" s="1" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A117" s="3"/>
       <c r="B117" s="3"/>
       <c r="C117" s="3"/>
@@ -3223,7 +2845,7 @@
       <c r="F117" s="3"/>
       <c r="G117" s="3"/>
       <c r="H117" s="3"/>
-      <c r="I117" s="1">
+      <c r="I117" s="1" t="n">
         <v>62</v>
       </c>
       <c r="J117" s="9" t="s">
@@ -3232,11 +2854,9 @@
       <c r="K117" s="11" t="s">
         <v>151</v>
       </c>
-      <c r="L117" s="3" t="s">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="118" s="1" customFormat="1" ht="15.65">
+      <c r="L117" s="3"/>
+    </row>
+    <row r="118" s="1" customFormat="true" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A118" s="3"/>
       <c r="B118" s="3"/>
       <c r="C118" s="3"/>
@@ -3247,7 +2867,7 @@
         <v>124</v>
       </c>
       <c r="H118" s="3"/>
-      <c r="I118" s="3">
+      <c r="I118" s="3" t="n">
         <v>63</v>
       </c>
       <c r="J118" s="7" t="s">
@@ -3256,11 +2876,9 @@
       <c r="K118" s="11" t="s">
         <v>153</v>
       </c>
-      <c r="L118" s="3" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="119" s="1" customFormat="1" ht="13.8">
+      <c r="L118" s="3"/>
+    </row>
+    <row r="119" s="1" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A119" s="3"/>
       <c r="B119" s="3"/>
       <c r="C119" s="3"/>
@@ -3269,7 +2887,7 @@
       <c r="F119" s="3"/>
       <c r="G119" s="3"/>
       <c r="H119" s="3"/>
-      <c r="I119" s="1">
+      <c r="I119" s="1" t="n">
         <v>64</v>
       </c>
       <c r="J119" s="9" t="s">
@@ -3278,11 +2896,9 @@
       <c r="K119" s="11" t="s">
         <v>155</v>
       </c>
-      <c r="L119" s="3" t="s">
-        <v>248</v>
-      </c>
-    </row>
-    <row r="120" s="1" customFormat="1" ht="15.65">
+      <c r="L119" s="3"/>
+    </row>
+    <row r="120" s="1" customFormat="true" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A120" s="3"/>
       <c r="B120" s="3"/>
       <c r="C120" s="3"/>
@@ -3293,7 +2909,7 @@
         <v>124</v>
       </c>
       <c r="H120" s="3"/>
-      <c r="I120" s="1">
+      <c r="I120" s="1" t="n">
         <v>65</v>
       </c>
       <c r="J120" s="10" t="s">
@@ -3302,11 +2918,9 @@
       <c r="K120" s="11" t="s">
         <v>157</v>
       </c>
-      <c r="L120" s="3" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="121" s="1" customFormat="1" ht="13.8">
+      <c r="L120" s="3"/>
+    </row>
+    <row r="121" s="1" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A121" s="3"/>
       <c r="B121" s="3"/>
       <c r="C121" s="3"/>
@@ -3315,7 +2929,7 @@
       <c r="F121" s="3"/>
       <c r="G121" s="12"/>
       <c r="H121" s="3"/>
-      <c r="I121" s="1">
+      <c r="I121" s="1" t="n">
         <v>66</v>
       </c>
       <c r="J121" s="10" t="s">
@@ -3324,11 +2938,9 @@
       <c r="K121" s="11" t="s">
         <v>159</v>
       </c>
-      <c r="L121" s="3" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="122" s="1" customFormat="1" ht="46.25">
+      <c r="L121" s="3"/>
+    </row>
+    <row r="122" s="1" customFormat="true" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A122" s="3"/>
       <c r="B122" s="3"/>
       <c r="C122" s="3"/>
@@ -3339,7 +2951,7 @@
         <v>124</v>
       </c>
       <c r="H122" s="3"/>
-      <c r="I122" s="1">
+      <c r="I122" s="1" t="n">
         <v>67</v>
       </c>
       <c r="J122" s="10" t="s">
@@ -3348,11 +2960,9 @@
       <c r="K122" s="11" t="s">
         <v>161</v>
       </c>
-      <c r="L122" s="3" t="s">
-        <v>251</v>
-      </c>
-    </row>
-    <row r="123" s="1" customFormat="1" ht="13.8">
+      <c r="L122" s="3"/>
+    </row>
+    <row r="123" s="1" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A123" s="3"/>
       <c r="B123" s="3"/>
       <c r="C123" s="3"/>
@@ -3361,7 +2971,7 @@
       <c r="F123" s="3"/>
       <c r="G123" s="12"/>
       <c r="H123" s="3"/>
-      <c r="I123" s="1">
+      <c r="I123" s="1" t="n">
         <v>68</v>
       </c>
       <c r="J123" s="10" t="s">
@@ -3370,11 +2980,9 @@
       <c r="K123" s="11" t="s">
         <v>163</v>
       </c>
-      <c r="L123" s="3" t="s">
-        <v>252</v>
-      </c>
-    </row>
-    <row r="124" s="1" customFormat="1" ht="23.85">
+      <c r="L123" s="3"/>
+    </row>
+    <row r="124" s="1" customFormat="true" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A124" s="3"/>
       <c r="B124" s="3"/>
       <c r="C124" s="3"/>
@@ -3385,7 +2993,7 @@
         <v>124</v>
       </c>
       <c r="H124" s="3"/>
-      <c r="I124" s="1">
+      <c r="I124" s="1" t="n">
         <v>69</v>
       </c>
       <c r="J124" s="10" t="s">
@@ -3394,11 +3002,9 @@
       <c r="K124" s="11" t="s">
         <v>165</v>
       </c>
-      <c r="L124" s="3" t="s">
-        <v>253</v>
-      </c>
-    </row>
-    <row r="125" s="1" customFormat="1" ht="13.8">
+      <c r="L124" s="3"/>
+    </row>
+    <row r="125" s="1" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A125" s="3"/>
       <c r="B125" s="3"/>
       <c r="C125" s="3"/>
@@ -3407,7 +3013,7 @@
       <c r="F125" s="3"/>
       <c r="G125" s="12"/>
       <c r="H125" s="3"/>
-      <c r="I125" s="1">
+      <c r="I125" s="1" t="n">
         <v>70</v>
       </c>
       <c r="J125" s="10" t="s">
@@ -3416,11 +3022,9 @@
       <c r="K125" s="11" t="s">
         <v>167</v>
       </c>
-      <c r="L125" s="3" t="s">
-        <v>254</v>
-      </c>
-    </row>
-    <row r="126" s="1" customFormat="1" ht="74.6">
+      <c r="L125" s="3"/>
+    </row>
+    <row r="126" s="1" customFormat="true" ht="74.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A126" s="3"/>
       <c r="B126" s="3"/>
       <c r="C126" s="3"/>
@@ -3431,7 +3035,7 @@
         <v>124</v>
       </c>
       <c r="H126" s="3"/>
-      <c r="I126" s="1">
+      <c r="I126" s="1" t="n">
         <v>71</v>
       </c>
       <c r="J126" s="10" t="s">
@@ -3440,11 +3044,9 @@
       <c r="K126" s="3" t="s">
         <v>169</v>
       </c>
-      <c r="L126" s="3" t="s">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="127" s="1" customFormat="1" ht="13.8">
+      <c r="L126" s="3"/>
+    </row>
+    <row r="127" s="1" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A127" s="3"/>
       <c r="B127" s="3"/>
       <c r="C127" s="3"/>
@@ -3453,7 +3055,7 @@
       <c r="F127" s="3"/>
       <c r="G127" s="12"/>
       <c r="H127" s="3"/>
-      <c r="I127" s="1">
+      <c r="I127" s="1" t="n">
         <v>72</v>
       </c>
       <c r="J127" s="10" t="s">
@@ -3462,11 +3064,9 @@
       <c r="K127" s="11" t="s">
         <v>171</v>
       </c>
-      <c r="L127" s="3" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="128" s="1" customFormat="1" ht="13.8">
+      <c r="L127" s="3"/>
+    </row>
+    <row r="128" s="1" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A128" s="3"/>
       <c r="B128" s="3"/>
       <c r="C128" s="3"/>
@@ -3481,7 +3081,7 @@
       <c r="K128" s="3"/>
       <c r="L128" s="3"/>
     </row>
-    <row r="129" s="1" customFormat="1" ht="15.65">
+    <row r="129" s="1" customFormat="true" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A129" s="3"/>
       <c r="B129" s="3"/>
       <c r="C129" s="3"/>
@@ -3492,7 +3092,7 @@
         <v>173</v>
       </c>
       <c r="H129" s="3"/>
-      <c r="I129" s="1">
+      <c r="I129" s="1" t="n">
         <v>73</v>
       </c>
       <c r="J129" s="10" t="s">
@@ -3501,11 +3101,9 @@
       <c r="K129" s="11" t="s">
         <v>171</v>
       </c>
-      <c r="L129" s="3" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="130" s="1" customFormat="1" ht="74.6">
+      <c r="L129" s="3"/>
+    </row>
+    <row r="130" s="1" customFormat="true" ht="74.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A130" s="3"/>
       <c r="B130" s="3"/>
       <c r="C130" s="3"/>
@@ -3516,7 +3114,7 @@
         <v>124</v>
       </c>
       <c r="H130" s="3"/>
-      <c r="I130" s="1">
+      <c r="I130" s="1" t="n">
         <v>74</v>
       </c>
       <c r="J130" s="10" t="s">
@@ -3525,11 +3123,9 @@
       <c r="K130" s="3" t="s">
         <v>175</v>
       </c>
-      <c r="L130" s="3" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="131" s="1" customFormat="1" ht="13.8">
+      <c r="L130" s="3"/>
+    </row>
+    <row r="131" s="1" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A131" s="3"/>
       <c r="B131" s="3"/>
       <c r="C131" s="3"/>
@@ -3538,7 +3134,7 @@
       <c r="F131" s="3"/>
       <c r="G131" s="12"/>
       <c r="H131" s="3"/>
-      <c r="I131" s="1">
+      <c r="I131" s="1" t="n">
         <v>75</v>
       </c>
       <c r="J131" s="10" t="s">
@@ -3547,11 +3143,9 @@
       <c r="K131" s="11" t="s">
         <v>177</v>
       </c>
-      <c r="L131" s="3" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="132" s="1" customFormat="1" ht="46.25">
+      <c r="L131" s="3"/>
+    </row>
+    <row r="132" s="1" customFormat="true" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A132" s="3"/>
       <c r="B132" s="3"/>
       <c r="C132" s="3"/>
@@ -3562,7 +3156,7 @@
         <v>124</v>
       </c>
       <c r="H132" s="3"/>
-      <c r="I132" s="1">
+      <c r="I132" s="1" t="n">
         <v>76</v>
       </c>
       <c r="J132" s="10" t="s">
@@ -3571,11 +3165,9 @@
       <c r="K132" s="3" t="s">
         <v>179</v>
       </c>
-      <c r="L132" s="3" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="133" s="1" customFormat="1" ht="13.8">
+      <c r="L132" s="3"/>
+    </row>
+    <row r="133" s="1" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A133" s="3"/>
       <c r="B133" s="3"/>
       <c r="C133" s="3"/>
@@ -3584,7 +3176,7 @@
       <c r="F133" s="3"/>
       <c r="G133" s="12"/>
       <c r="H133" s="3"/>
-      <c r="I133" s="1">
+      <c r="I133" s="1" t="n">
         <v>77</v>
       </c>
       <c r="J133" s="10" t="s">
@@ -3593,11 +3185,9 @@
       <c r="K133" s="11" t="s">
         <v>181</v>
       </c>
-      <c r="L133" s="3" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="134" s="1" customFormat="1" ht="15.65">
+      <c r="L133" s="3"/>
+    </row>
+    <row r="134" s="1" customFormat="true" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A134" s="3"/>
       <c r="B134" s="3"/>
       <c r="C134" s="3"/>
@@ -3608,7 +3198,7 @@
         <v>69</v>
       </c>
       <c r="H134" s="3"/>
-      <c r="I134" s="1">
+      <c r="I134" s="1" t="n">
         <v>78</v>
       </c>
       <c r="J134" s="10" t="s">
@@ -3617,11 +3207,9 @@
       <c r="K134" s="11" t="s">
         <v>183</v>
       </c>
-      <c r="L134" s="3" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="135" s="1" customFormat="1" ht="78.35">
+      <c r="L134" s="3"/>
+    </row>
+    <row r="135" s="1" customFormat="true" ht="78.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A135" s="3"/>
       <c r="B135" s="3"/>
       <c r="C135" s="3"/>
@@ -3632,7 +3220,7 @@
         <v>124</v>
       </c>
       <c r="H135" s="3"/>
-      <c r="I135" s="1">
+      <c r="I135" s="1" t="n">
         <v>79</v>
       </c>
       <c r="J135" s="10" t="s">
@@ -3641,11 +3229,9 @@
       <c r="K135" s="11" t="s">
         <v>185</v>
       </c>
-      <c r="L135" s="3" t="s">
-        <v>262</v>
-      </c>
-    </row>
-    <row r="136" s="1" customFormat="1" ht="78.35">
+      <c r="L135" s="3"/>
+    </row>
+    <row r="136" s="1" customFormat="true" ht="78.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A136" s="3"/>
       <c r="B136" s="3"/>
       <c r="C136" s="3"/>
@@ -3656,7 +3242,7 @@
         <v>124</v>
       </c>
       <c r="H136" s="3"/>
-      <c r="I136" s="1">
+      <c r="I136" s="1" t="n">
         <v>80</v>
       </c>
       <c r="J136" s="10" t="s">
@@ -3665,11 +3251,9 @@
       <c r="K136" s="11" t="s">
         <v>187</v>
       </c>
-      <c r="L136" s="3" t="s">
-        <v>263</v>
-      </c>
-    </row>
-    <row r="137" s="1" customFormat="1" ht="13.8">
+      <c r="L136" s="3"/>
+    </row>
+    <row r="137" s="1" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A137" s="3"/>
       <c r="B137" s="3"/>
       <c r="C137" s="3"/>
@@ -3678,7 +3262,7 @@
       <c r="F137" s="3"/>
       <c r="G137" s="12"/>
       <c r="H137" s="3"/>
-      <c r="I137" s="1">
+      <c r="I137" s="1" t="n">
         <v>81</v>
       </c>
       <c r="J137" s="10" t="s">
@@ -3687,11 +3271,9 @@
       <c r="K137" s="11" t="s">
         <v>189</v>
       </c>
-      <c r="L137" s="3" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="138" s="1" customFormat="1" ht="23.85">
+      <c r="L137" s="3"/>
+    </row>
+    <row r="138" s="1" customFormat="true" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A138" s="3"/>
       <c r="B138" s="3"/>
       <c r="C138" s="3"/>
@@ -3702,7 +3284,7 @@
         <v>124</v>
       </c>
       <c r="H138" s="3"/>
-      <c r="I138" s="1">
+      <c r="I138" s="1" t="n">
         <v>82</v>
       </c>
       <c r="J138" s="10" t="s">
@@ -3711,11 +3293,9 @@
       <c r="K138" s="11" t="s">
         <v>191</v>
       </c>
-      <c r="L138" s="3" t="s">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="139" s="1" customFormat="1" ht="13.8">
+      <c r="L138" s="3"/>
+    </row>
+    <row r="139" s="1" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A139" s="3"/>
       <c r="B139" s="3"/>
       <c r="C139" s="3"/>
@@ -3728,7 +3308,7 @@
       <c r="K139" s="3"/>
       <c r="L139" s="3"/>
     </row>
-    <row r="140" s="1" customFormat="1" ht="13.8">
+    <row r="140" s="1" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A140" s="3"/>
       <c r="B140" s="3"/>
       <c r="C140" s="3"/>
@@ -3741,7 +3321,7 @@
       <c r="K140" s="3"/>
       <c r="L140" s="3"/>
     </row>
-    <row r="141" s="1" customFormat="1" ht="13.8">
+    <row r="141" s="1" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A141" s="3"/>
       <c r="B141" s="3"/>
       <c r="C141" s="3"/>
@@ -3754,7 +3334,7 @@
       <c r="K141" s="3"/>
       <c r="L141" s="3"/>
     </row>
-    <row r="142" s="1" customFormat="1" ht="13.8">
+    <row r="142" s="1" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A142" s="3"/>
       <c r="B142" s="3"/>
       <c r="C142" s="3"/>
@@ -3767,7 +3347,7 @@
       <c r="K142" s="3"/>
       <c r="L142" s="3"/>
     </row>
-    <row r="143" s="1" customFormat="1" ht="13.8">
+    <row r="143" s="1" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A143" s="3"/>
       <c r="B143" s="3"/>
       <c r="C143" s="3"/>
@@ -3780,7 +3360,7 @@
       <c r="K143" s="3"/>
       <c r="L143" s="3"/>
     </row>
-    <row r="144" s="1" customFormat="1" ht="22.35">
+    <row r="144" s="1" customFormat="true" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A144" s="3"/>
       <c r="B144" s="3"/>
       <c r="C144" s="3"/>
@@ -3795,7 +3375,7 @@
       <c r="K144" s="3"/>
       <c r="L144" s="3"/>
     </row>
-    <row r="145" s="1" customFormat="1" ht="12.8">
+    <row r="145" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A145" s="3"/>
       <c r="B145" s="3"/>
       <c r="C145" s="3"/>
@@ -3808,7 +3388,7 @@
       <c r="K145" s="3"/>
       <c r="L145" s="3"/>
     </row>
-    <row r="146" s="1" customFormat="1" ht="12.8">
+    <row r="146" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A146" s="3"/>
       <c r="B146" s="3"/>
       <c r="C146" s="3"/>
@@ -3821,7 +3401,7 @@
       <c r="K146" s="3"/>
       <c r="L146" s="3"/>
     </row>
-    <row r="147" s="1" customFormat="1" ht="12.8">
+    <row r="147" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A147" s="3"/>
       <c r="B147" s="3"/>
       <c r="C147" s="3"/>
@@ -3836,7 +3416,7 @@
       <c r="K147" s="3"/>
       <c r="L147" s="3"/>
     </row>
-    <row r="148" s="1" customFormat="1" ht="12.8">
+    <row r="148" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A148" s="3"/>
       <c r="B148" s="3"/>
       <c r="C148" s="3"/>
@@ -3851,12 +3431,12 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="I4:I18 I20:I53 I119:I1048576 I55:I117">
-    <cfRule type="duplicateValues" dxfId="0" priority="2"/>
+    <cfRule type="duplicateValues" priority="2" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0"/>
   </conditionalFormatting>
-  <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" orientation="portrait" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader/>
     <oddFooter/>
   </headerFooter>

--- a/new original/_Lang_Chinese/Lang/CN/Dialog/Drama/quru.xlsx
+++ b/new original/_Lang_Chinese/Lang/CN/Dialog/Drama/quru.xlsx
@@ -2,25 +2,25 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <fileVersion appName="Calc"/>
-  <workbookPr backupFile="false" showObjects="all" date1904="false"/>
-  <workbookProtection/>
+  <workbookPr autoCompressPictures="1"/>
+  <workbookProtection lockStructure="0" lockWindows="0" lockRevision="0"/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+    <workbookView windowWidth="16384" windowHeight="8192" tabRatio="500"/>
   </bookViews>
   <sheets>
-    <sheet name="quru" sheetId="1" state="visible" r:id="rId3"/>
+    <sheet name="quru" sheetId="1" r:id="rId3"/>
   </sheets>
-  <calcPr iterateCount="100" refMode="R1C1" iterate="false" iterateDelta="0.001"/>
+  <calcPr calcMode="auto" fullCalcOnLoad="0" refMode="R1C1" iterate="0" iterateCount="100" iterateDelta="0.001" fullPrecision="1" calcCompleted="0" calcOnSave="0" concurrentCalc="0" forceFullCalc="0"/>
   <extLst>
-    <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
-      <loext:extCalcPr stringRefSyntax="CalcA1"/>
+    <ext uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
+      <loext:extCalcPr xmlns:loext="http://schemas.libreoffice.org/" stringRefSyntax="CalcA1"/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="267" uniqueCount="192">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="369" uniqueCount="266">
   <si>
     <t xml:space="preserve">step</t>
   </si>
@@ -721,6 +721,242 @@
   <si>
     <t xml:space="preserve">Ask "Kettle." It seems he is hiding many secrets from you all... Heh heh heh...</t>
   </si>
+  <si>
+    <t xml:space="preserve"/>
+  </si>
+  <si>
+    <t xml:space="preserve">怎么？</t>
+  </si>
+  <si>
+    <t xml:space="preserve">哼哼哼♪</t>
+  </si>
+  <si>
+    <t xml:space="preserve">唔，这欢快的哼歌声是从哪里来的…</t>
+  </si>
+  <si>
+    <t xml:space="preserve">呵呵，你很开心嘛，库罗茨亚。那是什么歌？</t>
+  </si>
+  <si>
+    <t xml:space="preserve">（无视）哼哼哼♪天蓝色的～♪</t>
+  </si>
+  <si>
+    <t xml:space="preserve">（嘎）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">库罗茨亚，那首歌……是法莉斯小姐教给你的么？</t>
+  </si>
+  <si>
+    <t xml:space="preserve">哼哼哼♪梦幻的～♪</t>
+  </si>
+  <si>
+    <t xml:space="preserve">不、不要啊…！</t>
+  </si>
+  <si>
+    <t xml:space="preserve">啊，不、不对…呃，不是说你唱得不好。只是那首歌实在是…</t>
+  </si>
+  <si>
+    <t xml:space="preserve">……如果那首歌传开了就麻烦了……对了，那首歌的题材其实根本不存在。梦幻天蓝郁金香，听着就很假不是吗？连孩子都不会相信有那种花。真是糟糕的歌啊，哈哈！</t>
+  </si>
+  <si>
+    <t xml:space="preserve">…诶？</t>
+  </si>
+  <si>
+    <t xml:space="preserve">…罗伊特尔你个笨蛋！</t>
+  </si>
+  <si>
+    <t xml:space="preserve">啊，等、等等库罗茨亚，别露出那么生气的表情…等、等下啊…！</t>
+  </si>
+  <si>
+    <t xml:space="preserve">难道…那个孩子真的相信有梦幻天蓝郁金香吗？不会吧……</t>
+  </si>
+  <si>
+    <t xml:space="preserve">摸摸，摸摸♪</t>
+  </si>
+  <si>
+    <t xml:space="preserve">姆啾！</t>
+  </si>
+  <si>
+    <t xml:space="preserve">嘿嘿，很痒吗，歌罗贡？</t>
+  </si>
+  <si>
+    <t xml:space="preserve">姆啾。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">摸摸，摸摸，摸摸，摸摸，摸摸♪</t>
+  </si>
+  <si>
+    <t xml:space="preserve">姆啾…姆啾！</t>
+  </si>
+  <si>
+    <t xml:space="preserve">嘿嘿，很痒吧，歌罗贡！</t>
+  </si>
+  <si>
+    <t xml:space="preserve">啊…？</t>
+  </si>
+  <si>
+    <t xml:space="preserve">有人的感觉…那边有人过来了。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">谁会在这个时间来呢？</t>
+  </si>
+  <si>
+    <t xml:space="preserve">此处是…</t>
+  </si>
+  <si>
+    <t xml:space="preserve">姆啾…？</t>
+  </si>
+  <si>
+    <t xml:space="preserve">…龙之子，还有灾眼的少女…这是怎么回事…？</t>
+  </si>
+  <si>
+    <t xml:space="preserve">那个男人…斗篷下面诡异的眼睛，不是人类……异形……
+歌罗贡，离他远点。去叫大家过来。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">呵呵…异形吗。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">有什么好笑的？</t>
+  </si>
+  <si>
+    <t xml:space="preserve">灾眼的「库罗茨亚」啊，汝还尚未察觉吗？汝体内蕴藏着古老的力量，那是能招致灾祸的古老的毁灭之力，汝亦为异形之一。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">你…你怎么知道我的事情…？</t>
+  </si>
+  <si>
+    <t xml:space="preserve">好疼！ 我知道了我知道了，小家伙，现在就过去，别拽我了…啊…你、你…你是谁啊？　</t>
+  </si>
+  <si>
+    <t xml:space="preserve">大伙都来了！</t>
+  </si>
+  <si>
+    <t xml:space="preserve">这个男人是…</t>
+  </si>
+  <si>
+    <t xml:space="preserve">嚯…传说中的龙，加上灾眼的魔女，还有「初代炼金术师」。呵呵，竟能全部聚集于此，让人有种置身于神话之中的感觉呢。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">等下，你认识这个家伙，凯特尔？</t>
+  </si>
+  <si>
+    <t xml:space="preserve">「凯特尔」…这就是你现在的名字吗。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">…大家不要担心。这个男人的名字是迪米塔斯，是「流放者」。他应该不会伤害我们。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">流放者…？</t>
+  </si>
+  <si>
+    <t xml:space="preserve">流放者是触及世界的禁忌，为了偿还自己的罪孽被神使役的可怜之人。而他，甚至被自己侍奉的神所抛弃。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">…汝还是一点没变。吾确实失去了自己的目的和存在的意义，只是四处徘徊而已。
+然而，呵呵……汝又是否找到那所谓的意义与目标呢？看来吾还太年轻，不足以理解那永恒的痛苦啊，「凯特尔」。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">我只是个随风漂泊的流浪炼金术师。可能会在旅途中找到自己的意义，也可能不会。
+迪米塔斯，能问问你造访这里的意图吗？</t>
+  </si>
+  <si>
+    <t xml:space="preserve">…有只自古潜藏在此的恶魔消失了。其名为特菲拉。
+吾不过是路过此处，顺道前来观察一番罢了。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">…不，不如说吾是被吸引而来的，飘荡在这片土地上的命运异味。被众神所抛弃的可怜、愚昧而又令人忌惮的孩童，将再度开启疯狂之宴。
+有趣，让吾暂且留于此处，静静观察一番吧。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">那个男人说的事情…</t>
+  </si>
+  <si>
+    <t xml:space="preserve">呜，在我脑海里挥之不去。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">我身体中沉睡的力量……</t>
+  </si>
+  <si>
+    <t xml:space="preserve">能招致灾祸的古老的毁灭之力</t>
+  </si>
+  <si>
+    <t xml:space="preserve">姆啾……</t>
+  </si>
+  <si>
+    <t xml:space="preserve">自从遇到凯特尔之后……不，应该说是自从和罗伊特尔他们一起生活开始，就很少做噩梦了。我也不需要去考虑自己到底是什么人了。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">但是……</t>
+  </si>
+  <si>
+    <t xml:space="preserve">歌罗贡，我…</t>
+  </si>
+  <si>
+    <t xml:space="preserve">睡不着吗，小姑娘。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">流放者迪米塔斯…</t>
+  </si>
+  <si>
+    <t xml:space="preserve">看起来汝还无法驾驭那眼中寄宿的力量。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">我的眼睛…你说什么？</t>
+  </si>
+  <si>
+    <t xml:space="preserve">呵呵…那光芒…赤红的灾厄之光，当它寄宿在汝的眼中，混沌将降临于世。灾眼之女，汝尚不知自身的宿命。然而，那时终将到来，正如那一日一般。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">…那天？</t>
+  </si>
+  <si>
+    <t xml:space="preserve">不懂吾之所指吗。汝应该还没忘记吧，汝村子里发生的惨剧。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">…为什么你会知道…我和你明明以前没见过。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">呵呵呵...是这样吗？
+连吾也是第一次见到如此诅咒。汝双眸中寄宿的赤色光芒，究竟是憎恨之焰，抑或是恍惚之光？
+一夜之间，汝之村落便…</t>
+  </si>
+  <si>
+    <t xml:space="preserve">住口！</t>
+  </si>
+  <si>
+    <t xml:space="preserve">那声音…不…竟让吾险些提起往昔之事…
+汝之力量…不错，吾等一直在密切关注着继承古老血脉的汝。
+少女啊，那一日，「凯特尔」救下汝之性命，汝以为那是巧合吗？</t>
+  </si>
+  <si>
+    <t xml:space="preserve">离我远点。我不想听你的话了。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">呵呵呵…汝实不知情。
+那人不过是利用尔等罢了。无论是救汝性命，还是如今让汝与龙相遇，一切不过是为了满足他的私欲而已。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">我才不相信呢。你讲的…全都是谎话！</t>
+  </si>
+  <si>
+    <t xml:space="preserve">姆啾！！</t>
+  </si>
+  <si>
+    <t xml:space="preserve">嚯…这只龙如此稚嫩…竟会回应愤怒之声，且能与人类心意如此相通，倒是有趣。
+钢铁龙的幼子…魔石…石之容器…
+呵呵呵，原来如此，事情竟是如此。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">夜已经深了。离去之前，再告诉汝一件事情吧，灾眼之女。
+那头幼龙「太小」了。它的成长被抑制了，或许是出于自身的意志，也可能遭到了某种外力。
+遗憾的告诉你，若如此下去，它恐怕活不长了</t>
+  </si>
+  <si>
+    <t xml:space="preserve">歌罗贡…？等下，你说的是什么意思！</t>
+  </si>
+  <si>
+    <t xml:space="preserve">去问「凯特尔」就好。看来，那个人向汝隐瞒了很多秘密…呵呵呵…</t>
+  </si>
 </sst>
 </file>
 
@@ -741,19 +977,19 @@
     <font>
       <sz val="10"/>
       <name val="Arial"/>
-      <family val="0"/>
+      <family/>
       <charset val="128"/>
     </font>
     <font>
       <sz val="10"/>
       <name val="Arial"/>
-      <family val="0"/>
+      <family/>
       <charset val="128"/>
     </font>
     <font>
       <sz val="10"/>
       <name val="Arial"/>
-      <family val="0"/>
+      <family/>
       <charset val="128"/>
     </font>
     <font>
@@ -766,7 +1002,7 @@
     <font>
       <sz val="11"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <family val="0"/>
+      <family/>
       <charset val="128"/>
     </font>
     <font>
@@ -813,7 +1049,7 @@
     </fill>
   </fills>
   <borders count="1">
-    <border diagonalUp="false" diagonalDown="false">
+    <border>
       <left/>
       <right/>
       <top/>
@@ -822,98 +1058,98 @@
     </border>
   </borders>
   <cellStyleXfs count="20">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment/>
+      <protection locked="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
   </cellStyleXfs>
   <cellXfs count="17">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="0">
+      <alignment/>
+      <protection locked="1"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyProtection="1">
+      <alignment/>
+      <protection locked="1"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment/>
+      <protection locked="1"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment wrapText="1"/>
+      <protection locked="1"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment/>
+      <protection locked="1"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment/>
+      <protection locked="1"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment/>
+      <protection locked="1"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment/>
+      <protection locked="1"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment wrapText="1"/>
+      <protection locked="1"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment wrapText="1"/>
+      <protection locked="1"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment wrapText="1"/>
+      <protection locked="1"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment wrapText="1"/>
+      <protection locked="1"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment wrapText="1"/>
+      <protection locked="1"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment wrapText="1"/>
+      <protection locked="1"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment wrapText="1"/>
+      <protection locked="1"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyProtection="1">
+      <alignment/>
+      <protection locked="1"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment/>
+      <protection locked="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -927,13 +1163,13 @@
   <dxfs count="1">
     <dxf>
       <font>
+        <color rgb="FFCC0000"/>
         <name val="游ゴシック"/>
+        <family val="2"/>
         <charset val="128"/>
-        <family val="2"/>
-        <color rgb="FFCC0000"/>
       </font>
       <fill>
-        <patternFill>
+        <patternFill patternType="solid">
           <bgColor rgb="FFFFCCCC"/>
         </patternFill>
       </fill>
@@ -1109,26 +1345,26 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <sheetPr>
+    <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:L148"/>
-  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="8.85"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="19.85"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="21.28"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="4" style="1" width="11.85"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="16.12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="11.7"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="8" style="1" width="7.09"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="60.76"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="1" width="53.28"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="1" width="9.06"/>
+    <col min="1" max="1" width="8.85" style="1" customWidth="1"/>
+    <col min="2" max="2" width="19.85" style="1" customWidth="1"/>
+    <col min="3" max="3" width="21.28" style="1" customWidth="1"/>
+    <col min="4" max="5" width="11.85" style="1" customWidth="1"/>
+    <col min="6" max="6" width="16.12" style="1" customWidth="1"/>
+    <col min="7" max="7" width="11.7" style="1" customWidth="1"/>
+    <col min="8" max="9" width="7.09" style="1" customWidth="1"/>
+    <col min="10" max="10" width="60.76" style="1" customWidth="1"/>
+    <col min="11" max="11" width="53.28" style="1" customWidth="1"/>
+    <col min="12" max="12" width="9.06" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" ht="12.8">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1166,24 +1402,24 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="I2" s="1" t="n">
-        <f aca="false">MAX(I4:I1048576)</f>
+    <row r="2" ht="12.8">
+      <c r="I2" s="1">
+        <f>MAX(I4:I1048576)</f>
         <v>82</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="5" ht="12.8">
       <c r="B5" s="1" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" ht="12.8">
       <c r="A7" s="1" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="I8" s="1" t="n">
+    <row r="8" ht="12.8">
+      <c r="I8" s="1">
         <v>1</v>
       </c>
       <c r="J8" s="3" t="s">
@@ -1192,12 +1428,15 @@
       <c r="K8" s="3" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L8" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="9" ht="12.8">
       <c r="J9" s="4"/>
       <c r="K9" s="4"/>
     </row>
-    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="10" ht="12.8">
       <c r="E10" s="1" t="s">
         <v>16</v>
       </c>
@@ -1205,22 +1444,22 @@
         <v>17</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="11" ht="12.8">
       <c r="E11" s="1" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="12" ht="12.8">
       <c r="E12" s="1" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="15" ht="12.8">
       <c r="A15" s="1" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="16" ht="12.8">
       <c r="E16" s="1" t="s">
         <v>21</v>
       </c>
@@ -1228,7 +1467,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="17" ht="12.8">
       <c r="E17" s="1" t="s">
         <v>23</v>
       </c>
@@ -1236,8 +1475,8 @@
         <v>24</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="I18" s="1" t="n">
+    <row r="18" ht="13.8">
+      <c r="I18" s="1">
         <v>2</v>
       </c>
       <c r="J18" s="6" t="s">
@@ -1246,12 +1485,15 @@
       <c r="K18" s="3" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="19" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L18" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="19" ht="13.8">
       <c r="G19" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="I19" s="1" t="n">
+      <c r="I19" s="1">
         <v>3</v>
       </c>
       <c r="J19" s="7" t="s">
@@ -1260,9 +1502,12 @@
       <c r="K19" s="3" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="20" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="I20" s="1" t="n">
+      <c r="L19" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="20" ht="13.8">
+      <c r="I20" s="1">
         <v>4</v>
       </c>
       <c r="J20" s="7" t="s">
@@ -1271,12 +1516,15 @@
       <c r="K20" s="3" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="21" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L20" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="21" ht="13.8">
       <c r="G21" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="I21" s="1" t="n">
+      <c r="I21" s="1">
         <v>5</v>
       </c>
       <c r="J21" s="7" t="s">
@@ -1285,9 +1533,12 @@
       <c r="K21" s="3" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="22" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="I22" s="1" t="n">
+      <c r="L21" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="22" ht="13.8">
+      <c r="I22" s="1">
         <v>6</v>
       </c>
       <c r="J22" s="7" t="s">
@@ -1296,12 +1547,15 @@
       <c r="K22" s="3" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="23" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L22" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="23" ht="13.8">
       <c r="G23" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="I23" s="1" t="n">
+      <c r="I23" s="1">
         <v>7</v>
       </c>
       <c r="J23" s="7" t="s">
@@ -1310,9 +1564,12 @@
       <c r="K23" s="1" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="24" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="I24" s="1" t="n">
+      <c r="L23" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="24" ht="13.8">
+      <c r="I24" s="1">
         <v>8</v>
       </c>
       <c r="J24" s="7" t="s">
@@ -1321,12 +1578,15 @@
       <c r="K24" s="3" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="25" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L24" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="25" ht="13.8">
       <c r="G25" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="I25" s="1" t="n">
+      <c r="I25" s="1">
         <v>9</v>
       </c>
       <c r="J25" s="7" t="s">
@@ -1335,9 +1595,12 @@
       <c r="K25" s="8" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="26" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="I26" s="1" t="n">
+      <c r="L25" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="26" ht="13.8">
+      <c r="I26" s="1">
         <v>10</v>
       </c>
       <c r="J26" s="7" t="s">
@@ -1346,12 +1609,15 @@
       <c r="K26" s="3" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="27" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L26" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="27" ht="13.8">
       <c r="G27" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="I27" s="1" t="n">
+      <c r="I27" s="1">
         <v>11</v>
       </c>
       <c r="J27" s="7" t="s">
@@ -1360,9 +1626,12 @@
       <c r="K27" s="1" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="28" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="I28" s="1" t="n">
+      <c r="L27" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="28" ht="13.8">
+      <c r="I28" s="1">
         <v>12</v>
       </c>
       <c r="J28" s="9" t="s">
@@ -1371,12 +1640,15 @@
       <c r="K28" s="3" t="s">
         <v>42</v>
       </c>
-    </row>
-    <row r="29" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L28" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="29" ht="22.35">
       <c r="G29" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="I29" s="1" t="n">
+      <c r="I29" s="1">
         <v>13</v>
       </c>
       <c r="J29" s="7" t="s">
@@ -1385,12 +1657,15 @@
       <c r="K29" s="3" t="s">
         <v>44</v>
       </c>
-    </row>
-    <row r="30" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L29" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="30" ht="43.25">
       <c r="G30" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="I30" s="1" t="n">
+      <c r="I30" s="1">
         <v>14</v>
       </c>
       <c r="J30" s="7" t="s">
@@ -1399,9 +1674,12 @@
       <c r="K30" s="3" t="s">
         <v>46</v>
       </c>
-    </row>
-    <row r="31" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="I31" s="1" t="n">
+      <c r="L30" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="31" ht="13.8">
+      <c r="I31" s="1">
         <v>15</v>
       </c>
       <c r="J31" s="10" t="s">
@@ -1410,12 +1688,15 @@
       <c r="K31" s="3" t="s">
         <v>42</v>
       </c>
-    </row>
-    <row r="32" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L31" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="32" ht="13.8">
       <c r="G32" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="I32" s="1" t="n">
+      <c r="I32" s="1">
         <v>16</v>
       </c>
       <c r="J32" s="7" t="s">
@@ -1424,9 +1705,12 @@
       <c r="K32" s="3" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="33" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="I33" s="1" t="n">
+      <c r="L32" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="33" ht="13.8">
+      <c r="I33" s="1">
         <v>17</v>
       </c>
       <c r="J33" s="7" t="s">
@@ -1435,12 +1719,15 @@
       <c r="K33" s="11" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="34" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L33" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="34" ht="13.8">
       <c r="G34" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="I34" s="1" t="n">
+      <c r="I34" s="1">
         <v>18</v>
       </c>
       <c r="J34" s="6" t="s">
@@ -1449,12 +1736,15 @@
       <c r="K34" s="1" t="s">
         <v>52</v>
       </c>
-    </row>
-    <row r="35" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L34" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="35" ht="13.8">
       <c r="G35" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="I35" s="1" t="n">
+      <c r="I35" s="1">
         <v>19</v>
       </c>
       <c r="J35" s="6" t="s">
@@ -1463,12 +1753,15 @@
       <c r="K35" s="3" t="s">
         <v>42</v>
       </c>
-    </row>
-    <row r="36" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L35" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="36" ht="13.8">
       <c r="G36" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="I36" s="1" t="n">
+      <c r="I36" s="1">
         <v>20</v>
       </c>
       <c r="J36" s="6" t="s">
@@ -1477,21 +1770,24 @@
       <c r="K36" s="1" t="s">
         <v>54</v>
       </c>
-    </row>
-    <row r="37" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L36" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="37" ht="13.8">
       <c r="J37" s="10"/>
     </row>
-    <row r="38" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="38" ht="12.8">
       <c r="E38" s="1" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="41" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="41" ht="12.8">
       <c r="E41" s="1" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="44" s="1" customFormat="true" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="44" s="1" customFormat="1" ht="22.35">
       <c r="A44" s="3" t="s">
         <v>57</v>
       </c>
@@ -1506,7 +1802,7 @@
       <c r="K44" s="3"/>
       <c r="L44" s="3"/>
     </row>
-    <row r="45" s="1" customFormat="true" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="45" s="1" customFormat="1" ht="15.65">
       <c r="A45" s="3"/>
       <c r="B45" s="3"/>
       <c r="C45" s="3"/>
@@ -1523,7 +1819,7 @@
       <c r="K45" s="3"/>
       <c r="L45" s="3"/>
     </row>
-    <row r="46" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="46" s="1" customFormat="1" ht="12.8">
       <c r="A46" s="3"/>
       <c r="B46" s="3"/>
       <c r="C46" s="3"/>
@@ -1540,7 +1836,7 @@
       <c r="K46" s="3"/>
       <c r="L46" s="3"/>
     </row>
-    <row r="47" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="47" s="1" customFormat="1" ht="12.8">
       <c r="A47" s="3"/>
       <c r="B47" s="3"/>
       <c r="C47" s="3"/>
@@ -1553,7 +1849,7 @@
       <c r="K47" s="3"/>
       <c r="L47" s="3"/>
     </row>
-    <row r="48" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="48" s="1" customFormat="1" ht="12.8">
       <c r="A48" s="3"/>
       <c r="B48" s="3"/>
       <c r="C48" s="3"/>
@@ -1570,7 +1866,7 @@
       <c r="K48" s="3"/>
       <c r="L48" s="3"/>
     </row>
-    <row r="49" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="49" s="1" customFormat="1" ht="12.8">
       <c r="A49" s="3"/>
       <c r="B49" s="3"/>
       <c r="C49" s="3"/>
@@ -1578,7 +1874,7 @@
       <c r="E49" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="F49" s="3" t="n">
+      <c r="F49" s="3">
         <v>2</v>
       </c>
       <c r="G49" s="3"/>
@@ -1587,7 +1883,7 @@
       <c r="K49" s="3"/>
       <c r="L49" s="3"/>
     </row>
-    <row r="50" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="50" s="1" customFormat="1" ht="12.8">
       <c r="A50" s="3"/>
       <c r="B50" s="3"/>
       <c r="C50" s="3"/>
@@ -1604,7 +1900,7 @@
       <c r="K50" s="3"/>
       <c r="L50" s="3"/>
     </row>
-    <row r="51" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="51" s="1" customFormat="1" ht="12.8">
       <c r="A51" s="3"/>
       <c r="B51" s="3"/>
       <c r="C51" s="3"/>
@@ -1612,7 +1908,7 @@
       <c r="E51" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="F51" s="15" t="n">
+      <c r="F51" s="15">
         <v>74</v>
       </c>
       <c r="G51" s="3"/>
@@ -1621,7 +1917,7 @@
       <c r="K51" s="3"/>
       <c r="L51" s="3"/>
     </row>
-    <row r="52" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="52" s="1" customFormat="1" ht="12.8">
       <c r="A52" s="3"/>
       <c r="B52" s="3"/>
       <c r="C52" s="3"/>
@@ -1629,7 +1925,7 @@
       <c r="E52" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="F52" s="3" t="n">
+      <c r="F52" s="3">
         <v>2</v>
       </c>
       <c r="G52" s="3"/>
@@ -1638,7 +1934,7 @@
       <c r="K52" s="3"/>
       <c r="L52" s="3"/>
     </row>
-    <row r="53" s="1" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="53" s="1" customFormat="1" ht="13.8">
       <c r="A53" s="3"/>
       <c r="B53" s="3"/>
       <c r="C53" s="3"/>
@@ -1647,7 +1943,7 @@
       <c r="F53" s="3"/>
       <c r="G53" s="3"/>
       <c r="H53" s="3"/>
-      <c r="I53" s="1" t="n">
+      <c r="I53" s="1">
         <v>21</v>
       </c>
       <c r="J53" s="10" t="s">
@@ -1656,9 +1952,11 @@
       <c r="K53" s="11" t="s">
         <v>68</v>
       </c>
-      <c r="L53" s="3"/>
-    </row>
-    <row r="54" s="1" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L53" s="3" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="54" s="1" customFormat="1" ht="13.8">
       <c r="A54" s="3"/>
       <c r="B54" s="3"/>
       <c r="C54" s="3"/>
@@ -1669,7 +1967,7 @@
         <v>69</v>
       </c>
       <c r="H54" s="3"/>
-      <c r="I54" s="3" t="n">
+      <c r="I54" s="3">
         <v>22</v>
       </c>
       <c r="J54" s="9" t="s">
@@ -1678,9 +1976,11 @@
       <c r="K54" s="11" t="s">
         <v>71</v>
       </c>
-      <c r="L54" s="3"/>
-    </row>
-    <row r="55" s="1" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L54" s="3" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="55" s="1" customFormat="1" ht="13.8">
       <c r="A55" s="3"/>
       <c r="B55" s="3"/>
       <c r="C55" s="3"/>
@@ -1689,7 +1989,7 @@
       <c r="F55" s="3"/>
       <c r="G55" s="3"/>
       <c r="H55" s="3"/>
-      <c r="I55" s="1" t="n">
+      <c r="I55" s="1">
         <v>23</v>
       </c>
       <c r="J55" s="9" t="s">
@@ -1698,9 +1998,11 @@
       <c r="K55" s="11" t="s">
         <v>73</v>
       </c>
-      <c r="L55" s="3"/>
-    </row>
-    <row r="56" s="1" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L55" s="3" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="56" s="1" customFormat="1" ht="13.8">
       <c r="A56" s="3"/>
       <c r="B56" s="3"/>
       <c r="C56" s="3"/>
@@ -1711,7 +2013,7 @@
         <v>69</v>
       </c>
       <c r="H56" s="3"/>
-      <c r="I56" s="1" t="n">
+      <c r="I56" s="1">
         <v>24</v>
       </c>
       <c r="J56" s="9" t="s">
@@ -1720,9 +2022,11 @@
       <c r="K56" s="11" t="s">
         <v>75</v>
       </c>
-      <c r="L56" s="3"/>
-    </row>
-    <row r="57" s="1" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L56" s="3" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="57" s="1" customFormat="1" ht="13.8">
       <c r="A57" s="3"/>
       <c r="B57" s="3"/>
       <c r="C57" s="3"/>
@@ -1731,7 +2035,7 @@
       <c r="F57" s="3"/>
       <c r="G57" s="3"/>
       <c r="H57" s="3"/>
-      <c r="I57" s="1" t="n">
+      <c r="I57" s="1">
         <v>25</v>
       </c>
       <c r="J57" s="9" t="s">
@@ -1740,9 +2044,11 @@
       <c r="K57" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="L57" s="3"/>
-    </row>
-    <row r="58" s="1" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L57" s="3" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="58" s="1" customFormat="1" ht="13.8">
       <c r="A58" s="3"/>
       <c r="B58" s="3"/>
       <c r="C58" s="3"/>
@@ -1753,7 +2059,7 @@
         <v>69</v>
       </c>
       <c r="H58" s="3"/>
-      <c r="I58" s="1" t="n">
+      <c r="I58" s="1">
         <v>26</v>
       </c>
       <c r="J58" s="9" t="s">
@@ -1762,9 +2068,11 @@
       <c r="K58" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="L58" s="3"/>
-    </row>
-    <row r="59" s="1" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L58" s="3" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="59" s="1" customFormat="1" ht="13.8">
       <c r="A59" s="3"/>
       <c r="B59" s="3"/>
       <c r="C59" s="3"/>
@@ -1773,7 +2081,7 @@
       <c r="F59" s="3"/>
       <c r="G59" s="3"/>
       <c r="H59" s="3"/>
-      <c r="I59" s="1" t="n">
+      <c r="I59" s="1">
         <v>27</v>
       </c>
       <c r="J59" s="10" t="s">
@@ -1782,9 +2090,11 @@
       <c r="K59" s="11" t="s">
         <v>77</v>
       </c>
-      <c r="L59" s="3"/>
-    </row>
-    <row r="60" s="1" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L59" s="3" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="60" s="1" customFormat="1" ht="13.8">
       <c r="A60" s="3"/>
       <c r="B60" s="3"/>
       <c r="C60" s="3"/>
@@ -1795,7 +2105,7 @@
         <v>69</v>
       </c>
       <c r="H60" s="3"/>
-      <c r="I60" s="1" t="n">
+      <c r="I60" s="1">
         <v>28</v>
       </c>
       <c r="J60" s="10" t="s">
@@ -1804,9 +2114,11 @@
       <c r="K60" s="11" t="s">
         <v>79</v>
       </c>
-      <c r="L60" s="3"/>
-    </row>
-    <row r="61" s="1" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L60" s="3" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="61" s="1" customFormat="1" ht="13.8">
       <c r="A61" s="3"/>
       <c r="B61" s="3"/>
       <c r="C61" s="3"/>
@@ -1815,7 +2127,7 @@
       <c r="F61" s="3"/>
       <c r="G61" s="3"/>
       <c r="H61" s="3"/>
-      <c r="I61" s="1" t="n">
+      <c r="I61" s="1">
         <v>29</v>
       </c>
       <c r="J61" s="9" t="s">
@@ -1824,9 +2136,11 @@
       <c r="K61" s="11" t="s">
         <v>81</v>
       </c>
-      <c r="L61" s="3"/>
-    </row>
-    <row r="62" s="1" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L61" s="3" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="62" s="1" customFormat="1" ht="13.8">
       <c r="A62" s="3"/>
       <c r="B62" s="3"/>
       <c r="C62" s="3"/>
@@ -1834,7 +2148,7 @@
       <c r="E62" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="F62" s="16" t="n">
+      <c r="F62" s="16">
         <v>3</v>
       </c>
       <c r="G62" s="3"/>
@@ -1843,7 +2157,7 @@
       <c r="K62" s="3"/>
       <c r="L62" s="3"/>
     </row>
-    <row r="63" s="1" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="63" s="1" customFormat="1" ht="13.8">
       <c r="A63" s="3"/>
       <c r="B63" s="3"/>
       <c r="C63" s="3"/>
@@ -1852,7 +2166,7 @@
       <c r="F63" s="3"/>
       <c r="G63" s="3"/>
       <c r="H63" s="3"/>
-      <c r="I63" s="1" t="n">
+      <c r="I63" s="1">
         <v>30</v>
       </c>
       <c r="J63" s="9" t="s">
@@ -1861,9 +2175,11 @@
       <c r="K63" s="11" t="s">
         <v>83</v>
       </c>
-      <c r="L63" s="3"/>
-    </row>
-    <row r="64" s="1" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L63" s="3" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="64" s="1" customFormat="1" ht="13.8">
       <c r="A64" s="3"/>
       <c r="B64" s="3"/>
       <c r="C64" s="3"/>
@@ -1872,7 +2188,7 @@
       <c r="F64" s="3"/>
       <c r="G64" s="3"/>
       <c r="H64" s="3"/>
-      <c r="I64" s="1" t="n">
+      <c r="I64" s="1">
         <v>31</v>
       </c>
       <c r="J64" s="9" t="s">
@@ -1881,9 +2197,11 @@
       <c r="K64" s="11" t="s">
         <v>85</v>
       </c>
-      <c r="L64" s="3"/>
-    </row>
-    <row r="65" s="1" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L64" s="3" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="65" s="1" customFormat="1" ht="13.8">
       <c r="A65" s="3"/>
       <c r="B65" s="3"/>
       <c r="C65" s="3"/>
@@ -1891,7 +2209,7 @@
       <c r="E65" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="F65" s="3" t="n">
+      <c r="F65" s="3">
         <v>1</v>
       </c>
       <c r="G65" s="3"/>
@@ -1900,7 +2218,7 @@
       <c r="K65" s="3"/>
       <c r="L65" s="3"/>
     </row>
-    <row r="66" s="1" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="66" s="1" customFormat="1" ht="13.8">
       <c r="A66" s="3"/>
       <c r="B66" s="3"/>
       <c r="C66" s="3"/>
@@ -1908,7 +2226,7 @@
       <c r="E66" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="F66" s="3" t="n">
+      <c r="F66" s="3">
         <v>1</v>
       </c>
       <c r="G66" s="3"/>
@@ -1917,7 +2235,7 @@
       <c r="K66" s="3"/>
       <c r="L66" s="3"/>
     </row>
-    <row r="67" s="1" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="67" s="1" customFormat="1" ht="13.8">
       <c r="A67" s="3"/>
       <c r="B67" s="3"/>
       <c r="C67" s="3"/>
@@ -1926,7 +2244,7 @@
       <c r="F67" s="3"/>
       <c r="G67" s="3"/>
       <c r="H67" s="3"/>
-      <c r="I67" s="1" t="n">
+      <c r="I67" s="1">
         <v>32</v>
       </c>
       <c r="J67" s="9" t="s">
@@ -1935,9 +2253,11 @@
       <c r="K67" s="11" t="s">
         <v>87</v>
       </c>
-      <c r="L67" s="3"/>
-    </row>
-    <row r="68" s="1" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L67" s="3" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="68" s="1" customFormat="1" ht="13.8">
       <c r="A68" s="3"/>
       <c r="B68" s="3"/>
       <c r="C68" s="3"/>
@@ -1954,7 +2274,7 @@
       <c r="K68" s="3"/>
       <c r="L68" s="3"/>
     </row>
-    <row r="69" s="1" customFormat="true" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="69" s="1" customFormat="1" ht="15.65">
       <c r="A69" s="3"/>
       <c r="B69" s="3"/>
       <c r="C69" s="3"/>
@@ -1965,7 +2285,7 @@
         <v>58</v>
       </c>
       <c r="H69" s="3"/>
-      <c r="I69" s="1" t="n">
+      <c r="I69" s="1">
         <v>33</v>
       </c>
       <c r="J69" s="9" t="s">
@@ -1974,9 +2294,11 @@
       <c r="K69" s="11" t="s">
         <v>90</v>
       </c>
-      <c r="L69" s="3"/>
-    </row>
-    <row r="70" s="1" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L69" s="3" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="70" s="1" customFormat="1" ht="13.8">
       <c r="A70" s="3"/>
       <c r="B70" s="3"/>
       <c r="C70" s="3"/>
@@ -1987,7 +2309,7 @@
         <v>69</v>
       </c>
       <c r="H70" s="3"/>
-      <c r="I70" s="1" t="n">
+      <c r="I70" s="1">
         <v>34</v>
       </c>
       <c r="J70" s="9" t="s">
@@ -1996,9 +2318,11 @@
       <c r="K70" s="11" t="s">
         <v>92</v>
       </c>
-      <c r="L70" s="3"/>
-    </row>
-    <row r="71" s="1" customFormat="true" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L70" s="3" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="71" s="1" customFormat="1" ht="15.65">
       <c r="A71" s="3"/>
       <c r="B71" s="3"/>
       <c r="C71" s="3"/>
@@ -2009,7 +2333,7 @@
         <v>58</v>
       </c>
       <c r="H71" s="3"/>
-      <c r="I71" s="1" t="n">
+      <c r="I71" s="1">
         <v>35</v>
       </c>
       <c r="J71" s="9" t="s">
@@ -2018,9 +2342,11 @@
       <c r="K71" s="11" t="s">
         <v>94</v>
       </c>
-      <c r="L71" s="3"/>
-    </row>
-    <row r="72" s="1" customFormat="true" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L71" s="3" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="72" s="1" customFormat="1" ht="43.25">
       <c r="A72" s="3"/>
       <c r="B72" s="3"/>
       <c r="C72" s="3"/>
@@ -2029,7 +2355,7 @@
       <c r="F72" s="3"/>
       <c r="G72" s="3"/>
       <c r="H72" s="3"/>
-      <c r="I72" s="1" t="n">
+      <c r="I72" s="1">
         <v>36</v>
       </c>
       <c r="J72" s="9" t="s">
@@ -2038,9 +2364,11 @@
       <c r="K72" s="3" t="s">
         <v>96</v>
       </c>
-      <c r="L72" s="3"/>
-    </row>
-    <row r="73" s="1" customFormat="true" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L72" s="3" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="73" s="1" customFormat="1" ht="15.65">
       <c r="A73" s="3"/>
       <c r="B73" s="3"/>
       <c r="C73" s="3"/>
@@ -2051,7 +2379,7 @@
         <v>58</v>
       </c>
       <c r="H73" s="3"/>
-      <c r="I73" s="1" t="n">
+      <c r="I73" s="1">
         <v>37</v>
       </c>
       <c r="J73" s="9" t="s">
@@ -2060,9 +2388,11 @@
       <c r="K73" s="11" t="s">
         <v>98</v>
       </c>
-      <c r="L73" s="3"/>
-    </row>
-    <row r="74" s="1" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L73" s="3" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="74" s="1" customFormat="1" ht="13.8">
       <c r="A74" s="3"/>
       <c r="B74" s="3"/>
       <c r="C74" s="3"/>
@@ -2071,7 +2401,7 @@
       <c r="F74" s="3"/>
       <c r="G74" s="3"/>
       <c r="H74" s="3"/>
-      <c r="I74" s="1" t="n">
+      <c r="I74" s="1">
         <v>38</v>
       </c>
       <c r="J74" s="9" t="s">
@@ -2080,9 +2410,11 @@
       <c r="K74" s="11" t="s">
         <v>100</v>
       </c>
-      <c r="L74" s="3"/>
-    </row>
-    <row r="75" s="1" customFormat="true" ht="37.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L74" s="3" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="75" s="1" customFormat="1" ht="37.3">
       <c r="A75" s="3"/>
       <c r="B75" s="3"/>
       <c r="C75" s="3"/>
@@ -2093,7 +2425,7 @@
         <v>58</v>
       </c>
       <c r="H75" s="3"/>
-      <c r="I75" s="1" t="n">
+      <c r="I75" s="1">
         <v>39</v>
       </c>
       <c r="J75" s="9" t="s">
@@ -2102,9 +2434,11 @@
       <c r="K75" s="11" t="s">
         <v>102</v>
       </c>
-      <c r="L75" s="3"/>
-    </row>
-    <row r="76" s="1" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L75" s="3" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="76" s="1" customFormat="1" ht="13.8">
       <c r="A76" s="3"/>
       <c r="B76" s="3"/>
       <c r="C76" s="3"/>
@@ -2113,7 +2447,7 @@
       <c r="F76" s="3"/>
       <c r="G76" s="3"/>
       <c r="H76" s="3"/>
-      <c r="I76" s="1" t="n">
+      <c r="I76" s="1">
         <v>40</v>
       </c>
       <c r="J76" s="9" t="s">
@@ -2122,9 +2456,11 @@
       <c r="K76" s="11" t="s">
         <v>104</v>
       </c>
-      <c r="L76" s="3"/>
-    </row>
-    <row r="77" s="1" customFormat="true" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L76" s="3" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="77" s="1" customFormat="1" ht="25.35">
       <c r="A77" s="3"/>
       <c r="B77" s="3"/>
       <c r="C77" s="3"/>
@@ -2135,7 +2471,7 @@
         <v>22</v>
       </c>
       <c r="H77" s="3"/>
-      <c r="I77" s="1" t="n">
+      <c r="I77" s="1">
         <v>41</v>
       </c>
       <c r="J77" s="9" t="s">
@@ -2144,9 +2480,11 @@
       <c r="K77" s="11" t="s">
         <v>106</v>
       </c>
-      <c r="L77" s="3"/>
-    </row>
-    <row r="78" s="1" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L77" s="3" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="78" s="1" customFormat="1" ht="13.8">
       <c r="A78" s="3"/>
       <c r="B78" s="3"/>
       <c r="C78" s="3"/>
@@ -2155,7 +2493,7 @@
       <c r="F78" s="3"/>
       <c r="G78" s="3"/>
       <c r="H78" s="3"/>
-      <c r="I78" s="1" t="n">
+      <c r="I78" s="1">
         <v>42</v>
       </c>
       <c r="J78" s="9" t="s">
@@ -2164,9 +2502,11 @@
       <c r="K78" s="11" t="s">
         <v>108</v>
       </c>
-      <c r="L78" s="3"/>
-    </row>
-    <row r="79" s="1" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L78" s="3" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="79" s="1" customFormat="1" ht="13.8">
       <c r="A79" s="3"/>
       <c r="B79" s="3"/>
       <c r="C79" s="3"/>
@@ -2177,7 +2517,7 @@
         <v>109</v>
       </c>
       <c r="H79" s="3"/>
-      <c r="I79" s="1" t="n">
+      <c r="I79" s="1">
         <v>43</v>
       </c>
       <c r="J79" s="9" t="s">
@@ -2186,9 +2526,11 @@
       <c r="K79" s="11" t="s">
         <v>111</v>
       </c>
-      <c r="L79" s="3"/>
-    </row>
-    <row r="80" s="1" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L79" s="3" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="80" s="1" customFormat="1" ht="13.8">
       <c r="A80" s="3"/>
       <c r="B80" s="3"/>
       <c r="C80" s="3"/>
@@ -2201,7 +2543,7 @@
       <c r="K80" s="3"/>
       <c r="L80" s="3"/>
     </row>
-    <row r="81" s="1" customFormat="true" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="81" s="1" customFormat="1" ht="25.35">
       <c r="A81" s="3"/>
       <c r="B81" s="3"/>
       <c r="C81" s="3"/>
@@ -2212,7 +2554,7 @@
         <v>58</v>
       </c>
       <c r="H81" s="3"/>
-      <c r="I81" s="1" t="n">
+      <c r="I81" s="1">
         <v>44</v>
       </c>
       <c r="J81" s="9" t="s">
@@ -2221,9 +2563,11 @@
       <c r="K81" s="11" t="s">
         <v>113</v>
       </c>
-      <c r="L81" s="3"/>
-    </row>
-    <row r="82" s="1" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L81" s="3" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="82" s="1" customFormat="1" ht="13.8">
       <c r="A82" s="3"/>
       <c r="B82" s="3"/>
       <c r="C82" s="3"/>
@@ -2234,7 +2578,7 @@
         <v>22</v>
       </c>
       <c r="H82" s="3"/>
-      <c r="I82" s="1" t="n">
+      <c r="I82" s="1">
         <v>45</v>
       </c>
       <c r="J82" s="10" t="s">
@@ -2243,9 +2587,11 @@
       <c r="K82" s="11" t="s">
         <v>115</v>
       </c>
-      <c r="L82" s="3"/>
-    </row>
-    <row r="83" s="1" customFormat="true" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L82" s="3" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="83" s="1" customFormat="1" ht="15.65">
       <c r="A83" s="3"/>
       <c r="B83" s="3"/>
       <c r="C83" s="3"/>
@@ -2256,7 +2602,7 @@
         <v>58</v>
       </c>
       <c r="H83" s="3"/>
-      <c r="I83" s="1" t="n">
+      <c r="I83" s="1">
         <v>46</v>
       </c>
       <c r="J83" s="9" t="s">
@@ -2265,9 +2611,11 @@
       <c r="K83" s="11" t="s">
         <v>117</v>
       </c>
-      <c r="L83" s="3"/>
-    </row>
-    <row r="84" s="1" customFormat="true" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L83" s="3" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="84" s="1" customFormat="1" ht="23.85">
       <c r="A84" s="3"/>
       <c r="B84" s="3"/>
       <c r="C84" s="3"/>
@@ -2278,7 +2626,7 @@
         <v>109</v>
       </c>
       <c r="H84" s="3"/>
-      <c r="I84" s="1" t="n">
+      <c r="I84" s="1">
         <v>47</v>
       </c>
       <c r="J84" s="10" t="s">
@@ -2287,9 +2635,11 @@
       <c r="K84" s="11" t="s">
         <v>119</v>
       </c>
-      <c r="L84" s="3"/>
-    </row>
-    <row r="85" s="1" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L84" s="3" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="85" s="1" customFormat="1" ht="13.8">
       <c r="A85" s="3"/>
       <c r="B85" s="3"/>
       <c r="C85" s="3"/>
@@ -2298,7 +2648,7 @@
       <c r="F85" s="3"/>
       <c r="G85" s="12"/>
       <c r="H85" s="3"/>
-      <c r="I85" s="1" t="n">
+      <c r="I85" s="1">
         <v>48</v>
       </c>
       <c r="J85" s="9" t="s">
@@ -2307,9 +2657,11 @@
       <c r="K85" s="11" t="s">
         <v>121</v>
       </c>
-      <c r="L85" s="3"/>
-    </row>
-    <row r="86" s="1" customFormat="true" ht="37.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L85" s="3" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="86" s="1" customFormat="1" ht="37.3">
       <c r="A86" s="3"/>
       <c r="B86" s="3"/>
       <c r="C86" s="3"/>
@@ -2320,7 +2672,7 @@
         <v>109</v>
       </c>
       <c r="H86" s="3"/>
-      <c r="I86" s="1" t="n">
+      <c r="I86" s="1">
         <v>49</v>
       </c>
       <c r="J86" s="9" t="s">
@@ -2329,9 +2681,11 @@
       <c r="K86" s="11" t="s">
         <v>123</v>
       </c>
-      <c r="L86" s="3"/>
-    </row>
-    <row r="87" s="1" customFormat="true" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L86" s="3" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="87" s="1" customFormat="1" ht="64.15">
       <c r="A87" s="3"/>
       <c r="B87" s="3"/>
       <c r="C87" s="3"/>
@@ -2342,7 +2696,7 @@
         <v>124</v>
       </c>
       <c r="H87" s="3"/>
-      <c r="I87" s="1" t="n">
+      <c r="I87" s="1">
         <v>50</v>
       </c>
       <c r="J87" s="10" t="s">
@@ -2351,9 +2705,11 @@
       <c r="K87" s="3" t="s">
         <v>126</v>
       </c>
-      <c r="L87" s="3"/>
-    </row>
-    <row r="88" s="1" customFormat="true" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L87" s="3" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="88" s="1" customFormat="1" ht="46.25">
       <c r="A88" s="3"/>
       <c r="B88" s="3"/>
       <c r="C88" s="3"/>
@@ -2364,7 +2720,7 @@
         <v>109</v>
       </c>
       <c r="H88" s="3"/>
-      <c r="I88" s="1" t="n">
+      <c r="I88" s="1">
         <v>51</v>
       </c>
       <c r="J88" s="10" t="s">
@@ -2373,9 +2729,11 @@
       <c r="K88" s="3" t="s">
         <v>128</v>
       </c>
-      <c r="L88" s="3"/>
-    </row>
-    <row r="89" s="1" customFormat="true" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L88" s="3" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="89" s="1" customFormat="1" ht="46.25">
       <c r="A89" s="3"/>
       <c r="B89" s="3"/>
       <c r="C89" s="3"/>
@@ -2386,7 +2744,7 @@
         <v>124</v>
       </c>
       <c r="H89" s="3"/>
-      <c r="I89" s="1" t="n">
+      <c r="I89" s="1">
         <v>52</v>
       </c>
       <c r="J89" s="10" t="s">
@@ -2395,9 +2753,11 @@
       <c r="K89" s="3" t="s">
         <v>130</v>
       </c>
-      <c r="L89" s="3"/>
-    </row>
-    <row r="90" s="1" customFormat="true" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L89" s="3" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="90" s="1" customFormat="1" ht="68.65">
       <c r="A90" s="3"/>
       <c r="B90" s="3"/>
       <c r="C90" s="3"/>
@@ -2408,7 +2768,7 @@
         <v>124</v>
       </c>
       <c r="H90" s="3"/>
-      <c r="I90" s="1" t="n">
+      <c r="I90" s="1">
         <v>53</v>
       </c>
       <c r="J90" s="10" t="s">
@@ -2417,9 +2777,11 @@
       <c r="K90" s="3" t="s">
         <v>132</v>
       </c>
-      <c r="L90" s="3"/>
-    </row>
-    <row r="91" s="1" customFormat="true" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L90" s="3" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="91" s="1" customFormat="1" ht="22.35">
       <c r="A91" s="3"/>
       <c r="B91" s="3"/>
       <c r="C91" s="3"/>
@@ -2434,7 +2796,7 @@
       <c r="K91" s="3"/>
       <c r="L91" s="3"/>
     </row>
-    <row r="92" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="92" s="1" customFormat="1" ht="12.8">
       <c r="A92" s="3"/>
       <c r="B92" s="3"/>
       <c r="C92" s="3"/>
@@ -2447,7 +2809,7 @@
       <c r="K92" s="3"/>
       <c r="L92" s="3"/>
     </row>
-    <row r="93" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="93" s="1" customFormat="1" ht="12.8">
       <c r="A93" s="3"/>
       <c r="B93" s="3"/>
       <c r="C93" s="3"/>
@@ -2455,7 +2817,7 @@
       <c r="E93" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="F93" s="14" t="n">
+      <c r="F93" s="14">
         <v>3</v>
       </c>
       <c r="G93" s="3"/>
@@ -2464,7 +2826,7 @@
       <c r="K93" s="3"/>
       <c r="L93" s="3"/>
     </row>
-    <row r="94" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="94" s="1" customFormat="1" ht="12.8">
       <c r="A94" s="3"/>
       <c r="B94" s="3"/>
       <c r="C94" s="3"/>
@@ -2479,7 +2841,7 @@
       <c r="K94" s="3"/>
       <c r="L94" s="3"/>
     </row>
-    <row r="95" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="95" s="1" customFormat="1" ht="12.8">
       <c r="A95" s="3"/>
       <c r="B95" s="3"/>
       <c r="C95" s="3"/>
@@ -2492,7 +2854,7 @@
       <c r="K95" s="3"/>
       <c r="L95" s="3"/>
     </row>
-    <row r="97" s="1" customFormat="true" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="97" s="1" customFormat="1" ht="22.35">
       <c r="A97" s="3" t="s">
         <v>133</v>
       </c>
@@ -2507,7 +2869,7 @@
       <c r="K97" s="3"/>
       <c r="L97" s="3"/>
     </row>
-    <row r="98" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="98" s="1" customFormat="1" ht="12.8">
       <c r="A98" s="3"/>
       <c r="B98" s="3"/>
       <c r="C98" s="3"/>
@@ -2524,7 +2886,7 @@
       <c r="K98" s="3"/>
       <c r="L98" s="3"/>
     </row>
-    <row r="99" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="99" ht="12.8">
       <c r="A99" s="3"/>
       <c r="B99" s="3"/>
       <c r="C99" s="3"/>
@@ -2541,7 +2903,7 @@
       <c r="K99" s="3"/>
       <c r="L99" s="3"/>
     </row>
-    <row r="100" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="100" ht="12.8">
       <c r="A100" s="3"/>
       <c r="B100" s="3"/>
       <c r="C100" s="3"/>
@@ -2549,7 +2911,7 @@
       <c r="E100" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="F100" s="3" t="n">
+      <c r="F100" s="3">
         <v>2</v>
       </c>
       <c r="G100" s="3"/>
@@ -2558,7 +2920,7 @@
       <c r="K100" s="3"/>
       <c r="L100" s="3"/>
     </row>
-    <row r="101" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="101" ht="12.8">
       <c r="A101" s="3"/>
       <c r="B101" s="3"/>
       <c r="C101" s="3"/>
@@ -2575,7 +2937,7 @@
       <c r="K101" s="3"/>
       <c r="L101" s="3"/>
     </row>
-    <row r="102" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="102" ht="12.8">
       <c r="A102" s="3"/>
       <c r="B102" s="3"/>
       <c r="C102" s="3"/>
@@ -2588,7 +2950,7 @@
       <c r="K102" s="3"/>
       <c r="L102" s="3"/>
     </row>
-    <row r="103" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="103" ht="12.8">
       <c r="A103" s="3"/>
       <c r="B103" s="3"/>
       <c r="C103" s="3"/>
@@ -2596,7 +2958,7 @@
       <c r="E103" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="F103" s="3" t="n">
+      <c r="F103" s="3">
         <v>2</v>
       </c>
       <c r="G103" s="3"/>
@@ -2605,7 +2967,7 @@
       <c r="K103" s="3"/>
       <c r="L103" s="3"/>
     </row>
-    <row r="104" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="104" s="1" customFormat="1" ht="12.8">
       <c r="A104" s="3"/>
       <c r="B104" s="3"/>
       <c r="C104" s="3"/>
@@ -2618,7 +2980,7 @@
       <c r="K104" s="3"/>
       <c r="L104" s="3"/>
     </row>
-    <row r="105" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="105" s="1" customFormat="1" ht="12.8">
       <c r="A105" s="3"/>
       <c r="B105" s="3"/>
       <c r="C105" s="3"/>
@@ -2631,7 +2993,7 @@
       <c r="K105" s="3"/>
       <c r="L105" s="3"/>
     </row>
-    <row r="106" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="106" s="1" customFormat="1" ht="12.8">
       <c r="A106" s="3"/>
       <c r="B106" s="3"/>
       <c r="C106" s="3"/>
@@ -2644,7 +3006,7 @@
       <c r="K106" s="3"/>
       <c r="L106" s="3"/>
     </row>
-    <row r="107" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="107" s="1" customFormat="1" ht="12.8">
       <c r="A107" s="3"/>
       <c r="B107" s="3"/>
       <c r="C107" s="3"/>
@@ -2657,7 +3019,7 @@
       <c r="K107" s="3"/>
       <c r="L107" s="3"/>
     </row>
-    <row r="108" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="108" s="1" customFormat="1" ht="12.8">
       <c r="A108" s="3"/>
       <c r="B108" s="3"/>
       <c r="C108" s="3"/>
@@ -2666,7 +3028,7 @@
       <c r="F108" s="3"/>
       <c r="G108" s="3"/>
       <c r="H108" s="3"/>
-      <c r="I108" s="1" t="n">
+      <c r="I108" s="1">
         <v>54</v>
       </c>
       <c r="J108" s="3" t="s">
@@ -2675,9 +3037,11 @@
       <c r="K108" s="11" t="s">
         <v>136</v>
       </c>
-      <c r="L108" s="3"/>
-    </row>
-    <row r="109" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L108" s="3" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="109" s="1" customFormat="1" ht="12.8">
       <c r="A109" s="3"/>
       <c r="B109" s="3"/>
       <c r="C109" s="3"/>
@@ -2686,7 +3050,7 @@
       <c r="F109" s="3"/>
       <c r="G109" s="3"/>
       <c r="H109" s="3"/>
-      <c r="I109" s="1" t="n">
+      <c r="I109" s="1">
         <v>55</v>
       </c>
       <c r="J109" s="3" t="s">
@@ -2695,9 +3059,11 @@
       <c r="K109" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="L109" s="3"/>
-    </row>
-    <row r="110" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L109" s="3" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="110" s="1" customFormat="1" ht="12.8">
       <c r="A110" s="3"/>
       <c r="B110" s="3"/>
       <c r="C110" s="3"/>
@@ -2706,7 +3072,7 @@
       <c r="F110" s="3"/>
       <c r="G110" s="3"/>
       <c r="H110" s="3"/>
-      <c r="I110" s="1" t="n">
+      <c r="I110" s="1">
         <v>56</v>
       </c>
       <c r="J110" s="3" t="s">
@@ -2715,9 +3081,11 @@
       <c r="K110" s="11" t="s">
         <v>138</v>
       </c>
-      <c r="L110" s="3"/>
-    </row>
-    <row r="111" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L110" s="3" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="111" s="1" customFormat="1" ht="12.8">
       <c r="A111" s="3"/>
       <c r="B111" s="3"/>
       <c r="C111" s="3"/>
@@ -2734,7 +3102,7 @@
       <c r="K111" s="3"/>
       <c r="L111" s="3"/>
     </row>
-    <row r="112" s="1" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="112" s="1" customFormat="1" ht="13.8">
       <c r="A112" s="3"/>
       <c r="B112" s="3"/>
       <c r="C112" s="3"/>
@@ -2743,7 +3111,7 @@
       <c r="F112" s="14"/>
       <c r="G112" s="3"/>
       <c r="H112" s="3"/>
-      <c r="I112" s="1" t="n">
+      <c r="I112" s="1">
         <v>57</v>
       </c>
       <c r="J112" s="9" t="s">
@@ -2752,9 +3120,11 @@
       <c r="K112" s="11" t="s">
         <v>141</v>
       </c>
-      <c r="L112" s="3"/>
-    </row>
-    <row r="113" s="1" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L112" s="3" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="113" s="1" customFormat="1" ht="13.8">
       <c r="A113" s="3"/>
       <c r="B113" s="3"/>
       <c r="C113" s="3"/>
@@ -2763,7 +3133,7 @@
       <c r="F113" s="3"/>
       <c r="G113" s="3"/>
       <c r="H113" s="3"/>
-      <c r="I113" s="1" t="n">
+      <c r="I113" s="1">
         <v>58</v>
       </c>
       <c r="J113" s="9" t="s">
@@ -2772,9 +3142,11 @@
       <c r="K113" s="11" t="s">
         <v>143</v>
       </c>
-      <c r="L113" s="3"/>
-    </row>
-    <row r="114" s="1" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L113" s="3" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="114" s="1" customFormat="1" ht="13.8">
       <c r="A114" s="3"/>
       <c r="B114" s="3"/>
       <c r="C114" s="3"/>
@@ -2785,7 +3157,7 @@
         <v>69</v>
       </c>
       <c r="H114" s="3"/>
-      <c r="I114" s="1" t="n">
+      <c r="I114" s="1">
         <v>59</v>
       </c>
       <c r="J114" s="9" t="s">
@@ -2794,9 +3166,11 @@
       <c r="K114" s="11" t="s">
         <v>145</v>
       </c>
-      <c r="L114" s="3"/>
-    </row>
-    <row r="115" s="1" customFormat="true" ht="37.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L114" s="3" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="115" s="1" customFormat="1" ht="37.3">
       <c r="A115" s="3"/>
       <c r="B115" s="3"/>
       <c r="C115" s="3"/>
@@ -2805,7 +3179,7 @@
       <c r="F115" s="3"/>
       <c r="G115" s="3"/>
       <c r="H115" s="3"/>
-      <c r="I115" s="1" t="n">
+      <c r="I115" s="1">
         <v>60</v>
       </c>
       <c r="J115" s="9" t="s">
@@ -2814,9 +3188,11 @@
       <c r="K115" s="11" t="s">
         <v>147</v>
       </c>
-      <c r="L115" s="3"/>
-    </row>
-    <row r="116" s="1" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L115" s="3" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="116" s="1" customFormat="1" ht="13.8">
       <c r="A116" s="3"/>
       <c r="B116" s="3"/>
       <c r="C116" s="3"/>
@@ -2825,7 +3201,7 @@
       <c r="F116" s="3"/>
       <c r="G116" s="3"/>
       <c r="H116" s="3"/>
-      <c r="I116" s="1" t="n">
+      <c r="I116" s="1">
         <v>61</v>
       </c>
       <c r="J116" s="9" t="s">
@@ -2834,9 +3210,11 @@
       <c r="K116" s="11" t="s">
         <v>149</v>
       </c>
-      <c r="L116" s="3"/>
-    </row>
-    <row r="117" s="1" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L116" s="3" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="117" s="1" customFormat="1" ht="13.8">
       <c r="A117" s="3"/>
       <c r="B117" s="3"/>
       <c r="C117" s="3"/>
@@ -2845,7 +3223,7 @@
       <c r="F117" s="3"/>
       <c r="G117" s="3"/>
       <c r="H117" s="3"/>
-      <c r="I117" s="1" t="n">
+      <c r="I117" s="1">
         <v>62</v>
       </c>
       <c r="J117" s="9" t="s">
@@ -2854,9 +3232,11 @@
       <c r="K117" s="11" t="s">
         <v>151</v>
       </c>
-      <c r="L117" s="3"/>
-    </row>
-    <row r="118" s="1" customFormat="true" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L117" s="3" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="118" s="1" customFormat="1" ht="15.65">
       <c r="A118" s="3"/>
       <c r="B118" s="3"/>
       <c r="C118" s="3"/>
@@ -2867,7 +3247,7 @@
         <v>124</v>
       </c>
       <c r="H118" s="3"/>
-      <c r="I118" s="3" t="n">
+      <c r="I118" s="3">
         <v>63</v>
       </c>
       <c r="J118" s="7" t="s">
@@ -2876,9 +3256,11 @@
       <c r="K118" s="11" t="s">
         <v>153</v>
       </c>
-      <c r="L118" s="3"/>
-    </row>
-    <row r="119" s="1" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L118" s="3" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="119" s="1" customFormat="1" ht="13.8">
       <c r="A119" s="3"/>
       <c r="B119" s="3"/>
       <c r="C119" s="3"/>
@@ -2887,7 +3269,7 @@
       <c r="F119" s="3"/>
       <c r="G119" s="3"/>
       <c r="H119" s="3"/>
-      <c r="I119" s="1" t="n">
+      <c r="I119" s="1">
         <v>64</v>
       </c>
       <c r="J119" s="9" t="s">
@@ -2896,9 +3278,11 @@
       <c r="K119" s="11" t="s">
         <v>155</v>
       </c>
-      <c r="L119" s="3"/>
-    </row>
-    <row r="120" s="1" customFormat="true" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L119" s="3" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="120" s="1" customFormat="1" ht="15.65">
       <c r="A120" s="3"/>
       <c r="B120" s="3"/>
       <c r="C120" s="3"/>
@@ -2909,7 +3293,7 @@
         <v>124</v>
       </c>
       <c r="H120" s="3"/>
-      <c r="I120" s="1" t="n">
+      <c r="I120" s="1">
         <v>65</v>
       </c>
       <c r="J120" s="10" t="s">
@@ -2918,9 +3302,11 @@
       <c r="K120" s="11" t="s">
         <v>157</v>
       </c>
-      <c r="L120" s="3"/>
-    </row>
-    <row r="121" s="1" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L120" s="3" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="121" s="1" customFormat="1" ht="13.8">
       <c r="A121" s="3"/>
       <c r="B121" s="3"/>
       <c r="C121" s="3"/>
@@ -2929,7 +3315,7 @@
       <c r="F121" s="3"/>
       <c r="G121" s="12"/>
       <c r="H121" s="3"/>
-      <c r="I121" s="1" t="n">
+      <c r="I121" s="1">
         <v>66</v>
       </c>
       <c r="J121" s="10" t="s">
@@ -2938,9 +3324,11 @@
       <c r="K121" s="11" t="s">
         <v>159</v>
       </c>
-      <c r="L121" s="3"/>
-    </row>
-    <row r="122" s="1" customFormat="true" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L121" s="3" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="122" s="1" customFormat="1" ht="46.25">
       <c r="A122" s="3"/>
       <c r="B122" s="3"/>
       <c r="C122" s="3"/>
@@ -2951,7 +3339,7 @@
         <v>124</v>
       </c>
       <c r="H122" s="3"/>
-      <c r="I122" s="1" t="n">
+      <c r="I122" s="1">
         <v>67</v>
       </c>
       <c r="J122" s="10" t="s">
@@ -2960,9 +3348,11 @@
       <c r="K122" s="11" t="s">
         <v>161</v>
       </c>
-      <c r="L122" s="3"/>
-    </row>
-    <row r="123" s="1" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L122" s="3" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="123" s="1" customFormat="1" ht="13.8">
       <c r="A123" s="3"/>
       <c r="B123" s="3"/>
       <c r="C123" s="3"/>
@@ -2971,7 +3361,7 @@
       <c r="F123" s="3"/>
       <c r="G123" s="12"/>
       <c r="H123" s="3"/>
-      <c r="I123" s="1" t="n">
+      <c r="I123" s="1">
         <v>68</v>
       </c>
       <c r="J123" s="10" t="s">
@@ -2980,9 +3370,11 @@
       <c r="K123" s="11" t="s">
         <v>163</v>
       </c>
-      <c r="L123" s="3"/>
-    </row>
-    <row r="124" s="1" customFormat="true" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L123" s="3" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="124" s="1" customFormat="1" ht="23.85">
       <c r="A124" s="3"/>
       <c r="B124" s="3"/>
       <c r="C124" s="3"/>
@@ -2993,7 +3385,7 @@
         <v>124</v>
       </c>
       <c r="H124" s="3"/>
-      <c r="I124" s="1" t="n">
+      <c r="I124" s="1">
         <v>69</v>
       </c>
       <c r="J124" s="10" t="s">
@@ -3002,9 +3394,11 @@
       <c r="K124" s="11" t="s">
         <v>165</v>
       </c>
-      <c r="L124" s="3"/>
-    </row>
-    <row r="125" s="1" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L124" s="3" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="125" s="1" customFormat="1" ht="13.8">
       <c r="A125" s="3"/>
       <c r="B125" s="3"/>
       <c r="C125" s="3"/>
@@ -3013,7 +3407,7 @@
       <c r="F125" s="3"/>
       <c r="G125" s="12"/>
       <c r="H125" s="3"/>
-      <c r="I125" s="1" t="n">
+      <c r="I125" s="1">
         <v>70</v>
       </c>
       <c r="J125" s="10" t="s">
@@ -3022,9 +3416,11 @@
       <c r="K125" s="11" t="s">
         <v>167</v>
       </c>
-      <c r="L125" s="3"/>
-    </row>
-    <row r="126" s="1" customFormat="true" ht="74.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L125" s="3" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="126" s="1" customFormat="1" ht="74.6">
       <c r="A126" s="3"/>
       <c r="B126" s="3"/>
       <c r="C126" s="3"/>
@@ -3035,7 +3431,7 @@
         <v>124</v>
       </c>
       <c r="H126" s="3"/>
-      <c r="I126" s="1" t="n">
+      <c r="I126" s="1">
         <v>71</v>
       </c>
       <c r="J126" s="10" t="s">
@@ -3044,9 +3440,11 @@
       <c r="K126" s="3" t="s">
         <v>169</v>
       </c>
-      <c r="L126" s="3"/>
-    </row>
-    <row r="127" s="1" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L126" s="3" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="127" s="1" customFormat="1" ht="13.8">
       <c r="A127" s="3"/>
       <c r="B127" s="3"/>
       <c r="C127" s="3"/>
@@ -3055,7 +3453,7 @@
       <c r="F127" s="3"/>
       <c r="G127" s="12"/>
       <c r="H127" s="3"/>
-      <c r="I127" s="1" t="n">
+      <c r="I127" s="1">
         <v>72</v>
       </c>
       <c r="J127" s="10" t="s">
@@ -3064,9 +3462,11 @@
       <c r="K127" s="11" t="s">
         <v>171</v>
       </c>
-      <c r="L127" s="3"/>
-    </row>
-    <row r="128" s="1" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L127" s="3" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="128" s="1" customFormat="1" ht="13.8">
       <c r="A128" s="3"/>
       <c r="B128" s="3"/>
       <c r="C128" s="3"/>
@@ -3081,7 +3481,7 @@
       <c r="K128" s="3"/>
       <c r="L128" s="3"/>
     </row>
-    <row r="129" s="1" customFormat="true" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="129" s="1" customFormat="1" ht="15.65">
       <c r="A129" s="3"/>
       <c r="B129" s="3"/>
       <c r="C129" s="3"/>
@@ -3092,7 +3492,7 @@
         <v>173</v>
       </c>
       <c r="H129" s="3"/>
-      <c r="I129" s="1" t="n">
+      <c r="I129" s="1">
         <v>73</v>
       </c>
       <c r="J129" s="10" t="s">
@@ -3101,9 +3501,11 @@
       <c r="K129" s="11" t="s">
         <v>171</v>
       </c>
-      <c r="L129" s="3"/>
-    </row>
-    <row r="130" s="1" customFormat="true" ht="74.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L129" s="3" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="130" s="1" customFormat="1" ht="74.6">
       <c r="A130" s="3"/>
       <c r="B130" s="3"/>
       <c r="C130" s="3"/>
@@ -3114,7 +3516,7 @@
         <v>124</v>
       </c>
       <c r="H130" s="3"/>
-      <c r="I130" s="1" t="n">
+      <c r="I130" s="1">
         <v>74</v>
       </c>
       <c r="J130" s="10" t="s">
@@ -3123,9 +3525,11 @@
       <c r="K130" s="3" t="s">
         <v>175</v>
       </c>
-      <c r="L130" s="3"/>
-    </row>
-    <row r="131" s="1" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L130" s="3" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="131" s="1" customFormat="1" ht="13.8">
       <c r="A131" s="3"/>
       <c r="B131" s="3"/>
       <c r="C131" s="3"/>
@@ -3134,7 +3538,7 @@
       <c r="F131" s="3"/>
       <c r="G131" s="12"/>
       <c r="H131" s="3"/>
-      <c r="I131" s="1" t="n">
+      <c r="I131" s="1">
         <v>75</v>
       </c>
       <c r="J131" s="10" t="s">
@@ -3143,9 +3547,11 @@
       <c r="K131" s="11" t="s">
         <v>177</v>
       </c>
-      <c r="L131" s="3"/>
-    </row>
-    <row r="132" s="1" customFormat="true" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L131" s="3" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="132" s="1" customFormat="1" ht="46.25">
       <c r="A132" s="3"/>
       <c r="B132" s="3"/>
       <c r="C132" s="3"/>
@@ -3156,7 +3562,7 @@
         <v>124</v>
       </c>
       <c r="H132" s="3"/>
-      <c r="I132" s="1" t="n">
+      <c r="I132" s="1">
         <v>76</v>
       </c>
       <c r="J132" s="10" t="s">
@@ -3165,9 +3571,11 @@
       <c r="K132" s="3" t="s">
         <v>179</v>
       </c>
-      <c r="L132" s="3"/>
-    </row>
-    <row r="133" s="1" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L132" s="3" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="133" s="1" customFormat="1" ht="13.8">
       <c r="A133" s="3"/>
       <c r="B133" s="3"/>
       <c r="C133" s="3"/>
@@ -3176,7 +3584,7 @@
       <c r="F133" s="3"/>
       <c r="G133" s="12"/>
       <c r="H133" s="3"/>
-      <c r="I133" s="1" t="n">
+      <c r="I133" s="1">
         <v>77</v>
       </c>
       <c r="J133" s="10" t="s">
@@ -3185,9 +3593,11 @@
       <c r="K133" s="11" t="s">
         <v>181</v>
       </c>
-      <c r="L133" s="3"/>
-    </row>
-    <row r="134" s="1" customFormat="true" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L133" s="3" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="134" s="1" customFormat="1" ht="15.65">
       <c r="A134" s="3"/>
       <c r="B134" s="3"/>
       <c r="C134" s="3"/>
@@ -3198,7 +3608,7 @@
         <v>69</v>
       </c>
       <c r="H134" s="3"/>
-      <c r="I134" s="1" t="n">
+      <c r="I134" s="1">
         <v>78</v>
       </c>
       <c r="J134" s="10" t="s">
@@ -3207,9 +3617,11 @@
       <c r="K134" s="11" t="s">
         <v>183</v>
       </c>
-      <c r="L134" s="3"/>
-    </row>
-    <row r="135" s="1" customFormat="true" ht="78.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L134" s="3" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="135" s="1" customFormat="1" ht="78.35">
       <c r="A135" s="3"/>
       <c r="B135" s="3"/>
       <c r="C135" s="3"/>
@@ -3220,7 +3632,7 @@
         <v>124</v>
       </c>
       <c r="H135" s="3"/>
-      <c r="I135" s="1" t="n">
+      <c r="I135" s="1">
         <v>79</v>
       </c>
       <c r="J135" s="10" t="s">
@@ -3229,9 +3641,11 @@
       <c r="K135" s="11" t="s">
         <v>185</v>
       </c>
-      <c r="L135" s="3"/>
-    </row>
-    <row r="136" s="1" customFormat="true" ht="78.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L135" s="3" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="136" s="1" customFormat="1" ht="78.35">
       <c r="A136" s="3"/>
       <c r="B136" s="3"/>
       <c r="C136" s="3"/>
@@ -3242,7 +3656,7 @@
         <v>124</v>
       </c>
       <c r="H136" s="3"/>
-      <c r="I136" s="1" t="n">
+      <c r="I136" s="1">
         <v>80</v>
       </c>
       <c r="J136" s="10" t="s">
@@ -3251,9 +3665,11 @@
       <c r="K136" s="11" t="s">
         <v>187</v>
       </c>
-      <c r="L136" s="3"/>
-    </row>
-    <row r="137" s="1" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L136" s="3" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="137" s="1" customFormat="1" ht="13.8">
       <c r="A137" s="3"/>
       <c r="B137" s="3"/>
       <c r="C137" s="3"/>
@@ -3262,7 +3678,7 @@
       <c r="F137" s="3"/>
       <c r="G137" s="12"/>
       <c r="H137" s="3"/>
-      <c r="I137" s="1" t="n">
+      <c r="I137" s="1">
         <v>81</v>
       </c>
       <c r="J137" s="10" t="s">
@@ -3271,9 +3687,11 @@
       <c r="K137" s="11" t="s">
         <v>189</v>
       </c>
-      <c r="L137" s="3"/>
-    </row>
-    <row r="138" s="1" customFormat="true" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L137" s="3" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="138" s="1" customFormat="1" ht="23.85">
       <c r="A138" s="3"/>
       <c r="B138" s="3"/>
       <c r="C138" s="3"/>
@@ -3284,7 +3702,7 @@
         <v>124</v>
       </c>
       <c r="H138" s="3"/>
-      <c r="I138" s="1" t="n">
+      <c r="I138" s="1">
         <v>82</v>
       </c>
       <c r="J138" s="10" t="s">
@@ -3293,9 +3711,11 @@
       <c r="K138" s="11" t="s">
         <v>191</v>
       </c>
-      <c r="L138" s="3"/>
-    </row>
-    <row r="139" s="1" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L138" s="3" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="139" s="1" customFormat="1" ht="13.8">
       <c r="A139" s="3"/>
       <c r="B139" s="3"/>
       <c r="C139" s="3"/>
@@ -3308,7 +3728,7 @@
       <c r="K139" s="3"/>
       <c r="L139" s="3"/>
     </row>
-    <row r="140" s="1" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="140" s="1" customFormat="1" ht="13.8">
       <c r="A140" s="3"/>
       <c r="B140" s="3"/>
       <c r="C140" s="3"/>
@@ -3321,7 +3741,7 @@
       <c r="K140" s="3"/>
       <c r="L140" s="3"/>
     </row>
-    <row r="141" s="1" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="141" s="1" customFormat="1" ht="13.8">
       <c r="A141" s="3"/>
       <c r="B141" s="3"/>
       <c r="C141" s="3"/>
@@ -3334,7 +3754,7 @@
       <c r="K141" s="3"/>
       <c r="L141" s="3"/>
     </row>
-    <row r="142" s="1" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="142" s="1" customFormat="1" ht="13.8">
       <c r="A142" s="3"/>
       <c r="B142" s="3"/>
       <c r="C142" s="3"/>
@@ -3347,7 +3767,7 @@
       <c r="K142" s="3"/>
       <c r="L142" s="3"/>
     </row>
-    <row r="143" s="1" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="143" s="1" customFormat="1" ht="13.8">
       <c r="A143" s="3"/>
       <c r="B143" s="3"/>
       <c r="C143" s="3"/>
@@ -3360,7 +3780,7 @@
       <c r="K143" s="3"/>
       <c r="L143" s="3"/>
     </row>
-    <row r="144" s="1" customFormat="true" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="144" s="1" customFormat="1" ht="22.35">
       <c r="A144" s="3"/>
       <c r="B144" s="3"/>
       <c r="C144" s="3"/>
@@ -3375,7 +3795,7 @@
       <c r="K144" s="3"/>
       <c r="L144" s="3"/>
     </row>
-    <row r="145" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="145" s="1" customFormat="1" ht="12.8">
       <c r="A145" s="3"/>
       <c r="B145" s="3"/>
       <c r="C145" s="3"/>
@@ -3388,7 +3808,7 @@
       <c r="K145" s="3"/>
       <c r="L145" s="3"/>
     </row>
-    <row r="146" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="146" s="1" customFormat="1" ht="12.8">
       <c r="A146" s="3"/>
       <c r="B146" s="3"/>
       <c r="C146" s="3"/>
@@ -3401,7 +3821,7 @@
       <c r="K146" s="3"/>
       <c r="L146" s="3"/>
     </row>
-    <row r="147" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="147" s="1" customFormat="1" ht="12.8">
       <c r="A147" s="3"/>
       <c r="B147" s="3"/>
       <c r="C147" s="3"/>
@@ -3416,7 +3836,7 @@
       <c r="K147" s="3"/>
       <c r="L147" s="3"/>
     </row>
-    <row r="148" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="148" s="1" customFormat="1" ht="12.8">
       <c r="A148" s="3"/>
       <c r="B148" s="3"/>
       <c r="C148" s="3"/>
@@ -3431,12 +3851,12 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="I4:I18 I20:I53 I119:I1048576 I55:I117">
-    <cfRule type="duplicateValues" priority="2" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="2"/>
   </conditionalFormatting>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" orientation="portrait" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter>
     <oddHeader/>
     <oddFooter/>
   </headerFooter>
